--- a/config/Master Price List - 2026.xlsx
+++ b/config/Master Price List - 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3217" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="818">
   <si>
     <t>Name</t>
   </si>
@@ -561,1906 +561,1909 @@
     <t>LMN40150726</t>
   </si>
   <si>
+    <t>Deer and Rabbit Spray, Big Sky, ea</t>
+  </si>
+  <si>
+    <t>NEW007</t>
+  </si>
+  <si>
+    <t>Deer and Rabbit Spray, Bozeman, ea</t>
+  </si>
+  <si>
+    <t>NEW008</t>
+  </si>
+  <si>
+    <t>Delivery (Install), Big Sky, ea</t>
+  </si>
+  <si>
+    <t>NEW009</t>
+  </si>
+  <si>
+    <t>Delivery, Big Sky, ea</t>
+  </si>
+  <si>
+    <t>Delivery (Install), Bozeman, ea</t>
+  </si>
+  <si>
+    <t>NEW010</t>
+  </si>
+  <si>
+    <t>Delivery, Bozeman, ea</t>
+  </si>
+  <si>
+    <t>Delivery (Maintenance), Big Sky, ea</t>
+  </si>
+  <si>
+    <t>Delivery (Maintenance), Bozeman, ea</t>
+  </si>
+  <si>
+    <t>Douglas Fir, 10', ea</t>
+  </si>
+  <si>
+    <t>LMN44279462</t>
+  </si>
+  <si>
+    <t>Douglas Fir, 6', ea</t>
+  </si>
+  <si>
+    <t>LMN44279620</t>
+  </si>
+  <si>
+    <t>Douglas Fir, 7', ea</t>
+  </si>
+  <si>
+    <t>LMN44279617</t>
+  </si>
+  <si>
+    <t>Douglas Fir, 8', ea</t>
+  </si>
+  <si>
+    <t>LMN44279455</t>
+  </si>
+  <si>
+    <t>Douglas Fir, 9', ea</t>
+  </si>
+  <si>
+    <t>LMN44279460</t>
+  </si>
+  <si>
+    <t>Drip Emitter, ea</t>
+  </si>
+  <si>
+    <t>LMN40150668</t>
+  </si>
+  <si>
+    <t>Dump Fee Big Sky, ea</t>
+  </si>
+  <si>
+    <t>LMN49034492</t>
+  </si>
+  <si>
+    <t>Debris Dump Fee Big Sky, ea</t>
+  </si>
+  <si>
+    <t>Dump Fee Bozeman, ea</t>
+  </si>
+  <si>
+    <t>NEW011</t>
+  </si>
+  <si>
+    <t>Debris Dump Fee Bozeman, ea</t>
+  </si>
+  <si>
+    <t>Edging, Aluminium, ft</t>
+  </si>
+  <si>
+    <t>LMN40150742</t>
+  </si>
+  <si>
+    <t>Edging, Aluminum Edging Corners, ea</t>
+  </si>
+  <si>
+    <t>LMN45549103</t>
+  </si>
+  <si>
+    <t>Aluminum Edging Corners, ea</t>
+  </si>
+  <si>
+    <t>Edging, Plastic, ea</t>
+  </si>
+  <si>
+    <t>NEW012</t>
+  </si>
+  <si>
+    <t>Edging, Steel 5" x 1/4", ft</t>
+  </si>
+  <si>
+    <t>LMN40150741</t>
+  </si>
+  <si>
+    <t>Edging, Steel 5" x 3/16", ft</t>
+  </si>
+  <si>
+    <t>LMN40150740</t>
+  </si>
+  <si>
+    <t>Erosion Control Blanket, straw, sf</t>
+  </si>
+  <si>
+    <t>LMN40150795</t>
+  </si>
+  <si>
+    <t>Fertilizer, Bagged, ea</t>
+  </si>
+  <si>
+    <t>LMN40150793</t>
+  </si>
+  <si>
+    <t>Fertilizer, Liquid, ea</t>
+  </si>
+  <si>
+    <t>NEW013</t>
+  </si>
+  <si>
+    <t>Fertilizer, Spikes, ea</t>
+  </si>
+  <si>
+    <t>NEW014</t>
+  </si>
+  <si>
+    <t>Filter Fabric, sf</t>
+  </si>
+  <si>
+    <t>LMN40150729</t>
+  </si>
+  <si>
+    <t>Flagstone, Dimensional Bluestone, sf</t>
+  </si>
+  <si>
+    <t>LMN40150713</t>
+  </si>
+  <si>
+    <t>Flagstone, Frontier, ton</t>
+  </si>
+  <si>
+    <t>LMN40150710</t>
+  </si>
+  <si>
+    <t>Flagstone, Mohave, ton</t>
+  </si>
+  <si>
+    <t>LMN40150712</t>
+  </si>
+  <si>
+    <t>Flagstone, Windsor Grey, ton</t>
+  </si>
+  <si>
+    <t>LMN40150711</t>
+  </si>
+  <si>
+    <t>Gravel, 3/4"- 2", yd</t>
+  </si>
+  <si>
+    <t>LMN40150723</t>
+  </si>
+  <si>
+    <t>Stone, 3/4" crushed/2" round sewer, yd</t>
+  </si>
+  <si>
+    <t>Hedge Shearing, hr</t>
+  </si>
+  <si>
+    <t>LMN49073499</t>
+  </si>
+  <si>
+    <t>hr</t>
+  </si>
+  <si>
+    <t>Herbicide, gal</t>
+  </si>
+  <si>
+    <t>LMN48941386</t>
+  </si>
+  <si>
+    <t>gal</t>
+  </si>
+  <si>
+    <t>Hose Bib Irrigation Timer, ea</t>
+  </si>
+  <si>
+    <t>LMN45407580</t>
+  </si>
+  <si>
+    <t>Hydromulch, Flexterra, #50 Bale, ea</t>
+  </si>
+  <si>
+    <t>LMN40150792</t>
+  </si>
+  <si>
+    <t>Hydromulch, Wood or Straw, #50 Bale, ea</t>
+  </si>
+  <si>
+    <t>LMN40150794</t>
+  </si>
+  <si>
+    <t>Insecticidal Soap, ea</t>
+  </si>
+  <si>
+    <t>NEW015</t>
+  </si>
+  <si>
+    <t>Irri-gator GT15 pump</t>
+  </si>
+  <si>
+    <t>LMN43624203</t>
+  </si>
+  <si>
+    <t>Lawn Fertilization/Weed Control, ea</t>
+  </si>
+  <si>
+    <t>NEW017</t>
+  </si>
+  <si>
+    <t>Mileage, ea</t>
+  </si>
+  <si>
+    <t>LMN42434662</t>
+  </si>
+  <si>
+    <t>Miscellaneous, 2M Supply, $</t>
+  </si>
+  <si>
+    <t>LMN40150672</t>
+  </si>
+  <si>
+    <t>Miscellaneous, Bulk Material, $</t>
+  </si>
+  <si>
+    <t>LMN40150736</t>
+  </si>
+  <si>
+    <t>Miscellaneous, Irrigation, $</t>
+  </si>
+  <si>
+    <t>NEW036</t>
+  </si>
+  <si>
+    <t>Irrigation, Misc, $</t>
+  </si>
+  <si>
+    <t>Miscellaneous, Lumber, Kenyon Noble Including Hardware, $</t>
+  </si>
+  <si>
+    <t>LMN40150746</t>
+  </si>
+  <si>
+    <t>Miscellaneous, Midland Supply, $</t>
+  </si>
+  <si>
+    <t>LMN40150671</t>
+  </si>
+  <si>
+    <t>Miscellaneous, Mountain Supply, $</t>
+  </si>
+  <si>
+    <t>LMN40150673</t>
+  </si>
+  <si>
+    <t>Mow/Weed Whack Big Sky, hr</t>
+  </si>
+  <si>
+    <t>LMN49034498</t>
+  </si>
+  <si>
+    <t>Mow/Weed Whack Bozeman, hr</t>
+  </si>
+  <si>
+    <t>LMN49067191</t>
+  </si>
+  <si>
+    <t>Mugo Pine, 15 gal/B&amp;B, ea</t>
+  </si>
+  <si>
+    <t>LMN40150772</t>
+  </si>
+  <si>
+    <t>Mulch Glue, gal</t>
+  </si>
+  <si>
+    <t>LMN49355335</t>
+  </si>
+  <si>
+    <t>Mulch, Shredded Cedar, Bagged, ea</t>
+  </si>
+  <si>
+    <t>LMN40150721</t>
+  </si>
+  <si>
+    <t>Mulch, Shredded Cedar, Bulk, yd</t>
+  </si>
+  <si>
+    <t>LMN40150716</t>
+  </si>
+  <si>
+    <t>Mulch, Soil Pep, Bagged, ea</t>
+  </si>
+  <si>
+    <t>LMN40150717</t>
+  </si>
+  <si>
+    <t>Mulch, Soil Pep, Bulk, yd</t>
+  </si>
+  <si>
+    <t>LMN40150722</t>
+  </si>
+  <si>
+    <t>NDS drain box, 12" Includes Grate and Inserts, ea</t>
+  </si>
+  <si>
+    <t>LMN40150735</t>
+  </si>
+  <si>
+    <t>NDS Drain Box, 9" Includes Grate and Inserts, ea</t>
+  </si>
+  <si>
+    <t>LMN40150734</t>
+  </si>
+  <si>
+    <t>Neem Oil, bottle, ea</t>
+  </si>
+  <si>
+    <t>NEW020</t>
+  </si>
+  <si>
+    <t>Netafim, ft</t>
+  </si>
+  <si>
+    <t>LMN40150664</t>
+  </si>
+  <si>
+    <t>Node, 1 Station, ea</t>
+  </si>
+  <si>
+    <t>LMN40150690</t>
+  </si>
+  <si>
+    <t>Node, 2 Station, ea</t>
+  </si>
+  <si>
+    <t>NEW037</t>
+  </si>
+  <si>
+    <t>Noxious weed control, hr</t>
+  </si>
+  <si>
+    <t>NEW021</t>
+  </si>
+  <si>
+    <t>Nozzle, MP Rotator, ea</t>
+  </si>
+  <si>
+    <t>LMN40150687</t>
+  </si>
+  <si>
+    <t>Nozzle, RVAN, ea</t>
+  </si>
+  <si>
+    <t>NEW038</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Paver Edge</t>
+  </si>
+  <si>
+    <t>LMN46147072</t>
+  </si>
+  <si>
+    <t>Ft</t>
+  </si>
+  <si>
+    <t>Paver, 2-3", sf</t>
+  </si>
+  <si>
+    <t>LMN43641020</t>
+  </si>
+  <si>
+    <t>Peony cages, new, ea</t>
+  </si>
+  <si>
+    <t>NEW022</t>
+  </si>
+  <si>
+    <t>Per Diem, daily, ea</t>
+  </si>
+  <si>
+    <t>NEW023</t>
+  </si>
+  <si>
+    <t>Per Diem, overnight, ea</t>
+  </si>
+  <si>
+    <t>NEW024</t>
+  </si>
+  <si>
+    <t>Perennial, 1 gal, ea</t>
+  </si>
+  <si>
+    <t>LMN40150784</t>
+  </si>
+  <si>
+    <t>Perennial, 2 gal, ea</t>
+  </si>
+  <si>
+    <t>LMN43636223</t>
+  </si>
+  <si>
+    <t>Perennial, 4", ea</t>
+  </si>
+  <si>
+    <t>NEW025</t>
+  </si>
+  <si>
+    <t>Perennial, Peony, ea</t>
+  </si>
+  <si>
+    <t>NEW026</t>
+  </si>
+  <si>
+    <t>Perennial, qt, ea</t>
+  </si>
+  <si>
+    <t>LMN46208579</t>
+  </si>
+  <si>
+    <t>Perennial, Woody 1 gal (Kinnick, Mahonia, Rabbitbrush), ea</t>
+  </si>
+  <si>
+    <t>LMN40150785</t>
+  </si>
+  <si>
+    <t>PGV Valve, ea</t>
+  </si>
+  <si>
+    <t>NEW046</t>
+  </si>
+  <si>
+    <t>PGV Valve</t>
+  </si>
+  <si>
+    <t>Pine, Austrian/Scotch/Ponderosa, 10', ea</t>
+  </si>
+  <si>
+    <t>LMN40150775</t>
+  </si>
+  <si>
+    <t>Pine, Austrian/Scotch/Ponderosa, 12', ea</t>
+  </si>
+  <si>
+    <t>LMN44245325</t>
+  </si>
+  <si>
+    <t>Pine, Austrian/Scotch/Ponderosa, 6', ea</t>
+  </si>
+  <si>
+    <t>LMN40150773</t>
+  </si>
+  <si>
+    <t>Pine, Austrian/Scotch/Ponderosa, 8', ea</t>
+  </si>
+  <si>
+    <t>LMN40150774</t>
+  </si>
+  <si>
+    <t>Plant, Misc, $</t>
+  </si>
+  <si>
+    <t>LMN40150787</t>
+  </si>
+  <si>
+    <t>Plants, Shrub, Miscellaneous, ea</t>
+  </si>
+  <si>
+    <t>NEW027</t>
+  </si>
+  <si>
+    <t>Poly Slip Fix, ea</t>
+  </si>
+  <si>
+    <t>NEW045</t>
+  </si>
+  <si>
+    <t>Potting soil, bag, ea</t>
+  </si>
+  <si>
+    <t>NEW028</t>
+  </si>
+  <si>
+    <t>Preene, bucket, ea</t>
+  </si>
+  <si>
+    <t>NEW049</t>
+  </si>
+  <si>
+    <t>Rain Sensor, ea</t>
+  </si>
+  <si>
+    <t>LMN40150703</t>
+  </si>
+  <si>
+    <t>Rainbird 1806</t>
+  </si>
+  <si>
+    <t>LMN42185596</t>
+  </si>
+  <si>
+    <t>Rainbird ESP-SM6 module</t>
+  </si>
+  <si>
+    <t>LMN44195431</t>
+  </si>
+  <si>
+    <t>Rainbird ESP4ME3</t>
+  </si>
+  <si>
+    <t>LMN44195430</t>
+  </si>
+  <si>
+    <t>Rebar, 1/2", ft</t>
+  </si>
+  <si>
+    <t>LMN40150739</t>
+  </si>
+  <si>
+    <t>Road Mix, (1" or 3"), yd</t>
+  </si>
+  <si>
+    <t>LMN40150727</t>
+  </si>
+  <si>
+    <t>Root Start, gal</t>
+  </si>
+  <si>
+    <t>NEW030</t>
+  </si>
+  <si>
+    <t>Roundup, gal</t>
+  </si>
+  <si>
+    <t>NEW031</t>
+  </si>
+  <si>
+    <t>Scree, Flatwillow, ton</t>
+  </si>
+  <si>
+    <t>LMN40150709</t>
+  </si>
+  <si>
+    <t>Seed Mix, Lawn, lb</t>
+  </si>
+  <si>
+    <t>LMN40150789</t>
+  </si>
+  <si>
+    <t>lb</t>
+  </si>
+  <si>
+    <t>Seed Mix, Native, lb</t>
+  </si>
+  <si>
+    <t>LMN40150790</t>
+  </si>
+  <si>
+    <t>Shrub, Deciduous 15 gal/B&amp;B, ea</t>
+  </si>
+  <si>
+    <t>LMN40150779</t>
+  </si>
+  <si>
+    <t>Shrub, Deciduous 2 gal, ea</t>
+  </si>
+  <si>
+    <t>LMN40150776</t>
+  </si>
+  <si>
+    <t>Shrub, Deciduous 5 gal, ea</t>
+  </si>
+  <si>
+    <t>LMN40150777</t>
+  </si>
+  <si>
+    <t>Shrub, Deciduous 7 gal, ea</t>
+  </si>
+  <si>
+    <t>LMN40150778</t>
+  </si>
+  <si>
+    <t>Shrub, Evergreen 15 gal/B&amp;B, ea</t>
+  </si>
+  <si>
+    <t>LMN40150783</t>
+  </si>
+  <si>
+    <t>Shrub, Evergreen 2 gal, ea</t>
+  </si>
+  <si>
+    <t>LMN40150780</t>
+  </si>
+  <si>
+    <t>Shrub, Evergreen 5 gal, ea</t>
+  </si>
+  <si>
+    <t>LMN40150781</t>
+  </si>
+  <si>
+    <t>Shrub, Evergreen 7/10 gal, ea</t>
+  </si>
+  <si>
+    <t>LMN40150782</t>
+  </si>
+  <si>
+    <t>Shrub, Multistem, 6-8', ea</t>
+  </si>
+  <si>
+    <t>LMN40150786</t>
+  </si>
+  <si>
+    <t>Spaghetti Pipe, ft</t>
+  </si>
+  <si>
+    <t>LMN40150669</t>
+  </si>
+  <si>
+    <t>Sprinkler, 1804, ea</t>
+  </si>
+  <si>
+    <t>NEW041</t>
+  </si>
+  <si>
+    <t>Sprinkler, 1812, ea</t>
+  </si>
+  <si>
+    <t>LMN40150688</t>
+  </si>
+  <si>
+    <t>Sprinkler, 3504, ea</t>
+  </si>
+  <si>
+    <t>LMN45473708</t>
+  </si>
+  <si>
+    <t>Sprinker, 3504, ea</t>
+  </si>
+  <si>
+    <t>Sprinkler, 5012, ea</t>
+  </si>
+  <si>
+    <t>LMN40150689</t>
+  </si>
+  <si>
+    <t>Sprinkler, Rainbird 3500, ea</t>
+  </si>
+  <si>
+    <t>NEW042</t>
+  </si>
+  <si>
+    <t>Spruce, 10', ea</t>
+  </si>
+  <si>
+    <t>LMN40150750</t>
+  </si>
+  <si>
+    <t>Spruce, 12', ea</t>
+  </si>
+  <si>
+    <t>LMN40150751</t>
+  </si>
+  <si>
+    <t>Spruce, 14', ea</t>
+  </si>
+  <si>
+    <t>LMN40150752</t>
+  </si>
+  <si>
+    <t>Spruce, 16', ea</t>
+  </si>
+  <si>
+    <t>LMN40150753</t>
+  </si>
+  <si>
+    <t>Spruce, 18', ea</t>
+  </si>
+  <si>
+    <t>LMN40150754</t>
+  </si>
+  <si>
+    <t>Spruce, 20', ea</t>
+  </si>
+  <si>
+    <t>LMN40150755</t>
+  </si>
+  <si>
+    <t>Spruce, 22', ea</t>
+  </si>
+  <si>
+    <t>LMN40150756</t>
+  </si>
+  <si>
+    <t>Spruce, 4', ea</t>
+  </si>
+  <si>
+    <t>LMN40150749</t>
+  </si>
+  <si>
+    <t>Spruce, 6', ea</t>
+  </si>
+  <si>
+    <t>LMN40150747</t>
+  </si>
+  <si>
+    <t>Spruce, 8', ea</t>
+  </si>
+  <si>
+    <t>LMN40150748</t>
+  </si>
+  <si>
+    <t>Stone, Rock bark or Equivalent, yd</t>
+  </si>
+  <si>
+    <t>LMN40150718</t>
+  </si>
+  <si>
+    <t>Swing Fittings, ea</t>
+  </si>
+  <si>
+    <t>LMN40150682</t>
+  </si>
+  <si>
+    <t>Swing Pipe, ft</t>
+  </si>
+  <si>
+    <t>LMN40150681</t>
+  </si>
+  <si>
+    <t>T-post, 6' Metal, ea</t>
+  </si>
+  <si>
+    <t>LMN40150743</t>
+  </si>
+  <si>
+    <t>Topsoil, yd</t>
+  </si>
+  <si>
+    <t>LMN40150715</t>
+  </si>
+  <si>
+    <t>Treads, Frontier, ton</t>
+  </si>
+  <si>
+    <t>LMN40150714</t>
+  </si>
+  <si>
+    <t>Twine, ft</t>
+  </si>
+  <si>
+    <t>NEW032</t>
+  </si>
+  <si>
+    <t>Valve Box 6" Round, ea</t>
+  </si>
+  <si>
+    <t>NEW051</t>
+  </si>
+  <si>
+    <t>Valve Box, 6'' Round, ea</t>
+  </si>
+  <si>
+    <t>Valve Box, 10" Round, ea</t>
+  </si>
+  <si>
+    <t>LMN40150678</t>
+  </si>
+  <si>
+    <t>Valve Box, 10'' Round, ea</t>
+  </si>
+  <si>
+    <t>Valve Box, Jumbo, ea</t>
+  </si>
+  <si>
+    <t>LMN40150677</t>
+  </si>
+  <si>
+    <t>Valve box, Normal Rectangular</t>
+  </si>
+  <si>
+    <t>NEW050</t>
+  </si>
+  <si>
+    <t>Valve Box, Rectangular, ea</t>
+  </si>
+  <si>
+    <t>Weedmat Pins, ea</t>
+  </si>
+  <si>
+    <t>NEW052</t>
+  </si>
+  <si>
+    <t>Weedmat, sf</t>
+  </si>
+  <si>
+    <t>LMN40150728</t>
+  </si>
+  <si>
+    <t>Wildflower Seed, lb</t>
+  </si>
+  <si>
+    <t>LMN40150791</t>
+  </si>
+  <si>
+    <t>Wire Nuts, 3M (pair), ea</t>
+  </si>
+  <si>
+    <t>LMN40150702</t>
+  </si>
+  <si>
+    <t>Wire Nuts, Snaplock, ea</t>
+  </si>
+  <si>
+    <t>LMN40150701</t>
+  </si>
+  <si>
+    <t>Wire, 2-wire Irrigation Control, ft</t>
+  </si>
+  <si>
+    <t>LMN40150699</t>
+  </si>
+  <si>
+    <t>Wire, Irrigation Control (10 Strand), ft</t>
+  </si>
+  <si>
+    <t>LMN40150698</t>
+  </si>
+  <si>
+    <t>Wire, 10-strand Irrigation Control, ft</t>
+  </si>
+  <si>
+    <t>Wire, Irrigation Control (13 Strand)</t>
+  </si>
+  <si>
+    <t>NEW054</t>
+  </si>
+  <si>
+    <t>Wire,13 Strand Irrigation Control, Ft</t>
+  </si>
+  <si>
+    <t>Wire, Irrigation Control (7 Strand)</t>
+  </si>
+  <si>
+    <t>NEW053</t>
+  </si>
+  <si>
+    <t>Wire, 7 Strand Irrigation Control, Ft</t>
+  </si>
+  <si>
+    <t>Wire, Landscaping Lighting 10 Gauge, ft</t>
+  </si>
+  <si>
+    <t>LMN40150700</t>
+  </si>
+  <si>
+    <t>Wood Tree Post, ea</t>
+  </si>
+  <si>
+    <t>LMN40150745</t>
+  </si>
+  <si>
+    <t>1" Poly Repair Bundle, ea</t>
+  </si>
+  <si>
+    <t>NEW055</t>
+  </si>
+  <si>
+    <t>1.25" Poly Repair Bundle, ea</t>
+  </si>
+  <si>
+    <t>NEW056</t>
+  </si>
+  <si>
+    <t>1.5" Poly Repair Bundle, ea</t>
+  </si>
+  <si>
+    <t>NEW057</t>
+  </si>
+  <si>
+    <t>Wire Splice Bundle (7 Strand), ea</t>
+  </si>
+  <si>
+    <t>NEW058</t>
+  </si>
+  <si>
+    <t>Wire Splice Bundle (10 Strand), ea</t>
+  </si>
+  <si>
+    <t>NEW059</t>
+  </si>
+  <si>
+    <t>Wire Splice Bundle (13 Strand), ea</t>
+  </si>
+  <si>
+    <t>NEW060</t>
+  </si>
+  <si>
+    <t>Product/Service Name</t>
+  </si>
+  <si>
+    <t>Variant Name</t>
+  </si>
+  <si>
+    <t>Quantity on hand</t>
+  </si>
+  <si>
+    <t>Item type</t>
+  </si>
+  <si>
+    <t>Single,parent or variant?</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Income Account</t>
+  </si>
+  <si>
+    <t>Expense Account</t>
+  </si>
+  <si>
+    <t>Inventory asset account</t>
+  </si>
+  <si>
+    <t>Sales Description</t>
+  </si>
+  <si>
+    <t>Purchase Description</t>
+  </si>
+  <si>
+    <t>Reorder Point</t>
+  </si>
+  <si>
+    <t>Column 1</t>
+  </si>
+  <si>
+    <t>Non-inventory</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Irrigation Materials</t>
+  </si>
+  <si>
+    <t>1.5" Poly Fitting</t>
+  </si>
+  <si>
+    <t>1.5" Poly</t>
+  </si>
+  <si>
+    <t>1.5" Stretch Repair Coupling</t>
+  </si>
+  <si>
+    <t>1.5" Tie-In Assembly</t>
+  </si>
+  <si>
+    <t>1" Drip Valve</t>
+  </si>
+  <si>
+    <t>1" Fitting</t>
+  </si>
+  <si>
+    <t>1" Poly</t>
+  </si>
+  <si>
+    <t>1" Tie-In Assembly</t>
+  </si>
+  <si>
+    <t>1" Valve</t>
+  </si>
+  <si>
+    <t>1/2" Fitting</t>
+  </si>
+  <si>
+    <t>1/2" Poly</t>
+  </si>
+  <si>
+    <t>2" Poly Fitting</t>
+  </si>
+  <si>
+    <t>2" Poly</t>
+  </si>
+  <si>
+    <t>2" PVC Fitting</t>
+  </si>
+  <si>
+    <t>2" Stretch Repair Coupling</t>
+  </si>
+  <si>
+    <t>3/4" Brass Quick Coupler</t>
+  </si>
+  <si>
+    <t>Landscaping Materials</t>
+  </si>
+  <si>
+    <t>Drainage Materials</t>
+  </si>
+  <si>
+    <t>4" Corrugated Drain Pipe</t>
+  </si>
+  <si>
+    <t>4" Corrugated Fitting</t>
+  </si>
+  <si>
+    <t>4" PVC Sewer Fitting</t>
+  </si>
+  <si>
+    <t>4" PVC Sewer Pipe</t>
+  </si>
+  <si>
+    <t>5004 with Street L</t>
+  </si>
+  <si>
+    <t>800M4 Backflow</t>
+  </si>
+  <si>
+    <t>Action Fitting</t>
+  </si>
+  <si>
+    <t>Action Manifold</t>
+  </si>
+  <si>
+    <t>Plants</t>
+  </si>
+  <si>
+    <t>Trees</t>
+  </si>
+  <si>
+    <t>Alpine Fir, 10'</t>
+  </si>
+  <si>
+    <t>Alpine Fir, 12'</t>
+  </si>
+  <si>
+    <t>Annuals</t>
+  </si>
+  <si>
+    <t>Annual Flower Pot, 1 Gal</t>
+  </si>
+  <si>
+    <t>Annual Flower Pot, 1 Qt</t>
+  </si>
+  <si>
+    <t>Annual Flower Pot, 4"</t>
+  </si>
+  <si>
+    <t>Landscape Materials</t>
+  </si>
+  <si>
+    <t>Arbor Tie</t>
+  </si>
+  <si>
+    <t>Aspen, 2.5", Mulit Stem</t>
+  </si>
+  <si>
+    <t>Aspen, 2.5", Single Stem</t>
+  </si>
+  <si>
+    <t>Aspen, 2", Mulit Stem</t>
+  </si>
+  <si>
+    <t>Aspen, 2", Single Stem</t>
+  </si>
+  <si>
+    <t>Aspen, 3.5", Single Stem</t>
+  </si>
+  <si>
+    <t>Aspen, 3", Mulit Stem</t>
+  </si>
+  <si>
+    <t>Aspen, 3", Single Stem</t>
+  </si>
+  <si>
+    <t>Aspen, 4.5", Single Stem</t>
+  </si>
+  <si>
+    <t>Aspen, 4", Single Stem</t>
+  </si>
+  <si>
+    <t>Hardscape Materials</t>
+  </si>
+  <si>
+    <t>Belgard Pavers</t>
+  </si>
+  <si>
+    <t>Blazing Saddles</t>
+  </si>
+  <si>
+    <t>Boulder, Quarry Works</t>
+  </si>
+  <si>
+    <t>Bristlecone Pine, 6'</t>
+  </si>
+  <si>
+    <t>Bubbler</t>
+  </si>
+  <si>
+    <t>Bulbs</t>
+  </si>
+  <si>
+    <t>Bulb</t>
+  </si>
+  <si>
+    <t>Bulk</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Caging, linear</t>
+  </si>
+  <si>
+    <t>Gravel</t>
+  </si>
+  <si>
+    <t>Cobble</t>
+  </si>
+  <si>
+    <t>Landscape Installation</t>
+  </si>
+  <si>
+    <t>Compost, Bagged</t>
+  </si>
+  <si>
+    <t>Compost, Bulk</t>
+  </si>
+  <si>
+    <t>Concrete</t>
+  </si>
+  <si>
+    <t>Concrete Delivered</t>
+  </si>
+  <si>
+    <t>Concrete, Bagged</t>
+  </si>
+  <si>
+    <t>Controller, Hunter HPC 400</t>
+  </si>
+  <si>
+    <t>Controller, Hunter HPC Module</t>
+  </si>
+  <si>
+    <t>Controller, Hunter Icore Dual (2 wire)</t>
+  </si>
+  <si>
+    <t>Controller, Rainbird ESP ME</t>
+  </si>
+  <si>
+    <t>Controller, Rainbird ESP Module</t>
+  </si>
+  <si>
+    <t>Crimp Rings</t>
+  </si>
+  <si>
+    <t>Crusher Fines</t>
+  </si>
+  <si>
+    <t>DC Solenoid</t>
+  </si>
+  <si>
+    <t>Deciduous Cottonwood, 2.5"</t>
+  </si>
+  <si>
+    <t>Deciduous Cottonwood, 2"</t>
+  </si>
+  <si>
+    <t>Deciduous Cottonwood, 3"</t>
+  </si>
+  <si>
+    <t>Deciduous Shade/Fruit, 2.5"</t>
+  </si>
+  <si>
+    <t>Deciduous Shade/Fruit, 2"</t>
+  </si>
+  <si>
+    <t>Deciduous Shade/Fruit, 3"</t>
+  </si>
+  <si>
+    <t>Decoder, Hunter Icore</t>
+  </si>
+  <si>
+    <t>Decomposed Granite</t>
+  </si>
+  <si>
+    <t>Deer Spray</t>
+  </si>
+  <si>
+    <t>Fees</t>
+  </si>
+  <si>
+    <t>Delivery</t>
+  </si>
+  <si>
+    <t>Delivery, Big Sky</t>
+  </si>
+  <si>
+    <t>Delivery, Bozeman</t>
+  </si>
+  <si>
+    <t>Douglas Fir, 10'</t>
+  </si>
+  <si>
+    <t>Douglas Fir, 6'</t>
+  </si>
+  <si>
+    <t>Douglas Fir, 7'</t>
+  </si>
+  <si>
+    <t>Douglas Fir, 8'</t>
+  </si>
+  <si>
+    <t>Douglas Fir, 9'</t>
+  </si>
+  <si>
+    <t>Drip Emitter</t>
+  </si>
+  <si>
+    <t>Dump</t>
+  </si>
+  <si>
+    <t>Edging</t>
+  </si>
+  <si>
+    <t>Edging, Plastic 20', ea</t>
+  </si>
+  <si>
+    <t>Edging, Steel 5"x1/4", ft</t>
+  </si>
+  <si>
+    <t>Seeding</t>
+  </si>
+  <si>
+    <t>Fertilizer</t>
+  </si>
+  <si>
+    <t>Fertilizer, Liquid</t>
+  </si>
+  <si>
+    <t>Fertilizer, Spikes</t>
+  </si>
+  <si>
+    <t>Maintenance:Lawn Care</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>Herbicide</t>
+  </si>
+  <si>
+    <t>Hose Bib Irrigation Timer</t>
+  </si>
+  <si>
+    <t>Hydromulch, Flexterra, #50 Bale</t>
+  </si>
+  <si>
+    <t>Hydromulch, Wood or Straw, #50 Bale</t>
+  </si>
+  <si>
+    <t>Insecticidal Soap</t>
+  </si>
+  <si>
+    <t>Lawn Service, ea</t>
+  </si>
+  <si>
+    <t>Mileage</t>
+  </si>
+  <si>
+    <t>Miscellaneous, 2M Supply</t>
+  </si>
+  <si>
+    <t>Miscellaneous, Bulk Material</t>
+  </si>
+  <si>
+    <t>Miscellaneous, Irrigation</t>
+  </si>
+  <si>
+    <t>Miscellaneous, Lumber, Kenyon Noble Including Hardware</t>
+  </si>
+  <si>
+    <t>Miscellaneous, Midland Supply</t>
+  </si>
+  <si>
+    <t>Miscellaneous, Mountain Supply</t>
+  </si>
+  <si>
+    <t>Shrubs</t>
+  </si>
+  <si>
+    <t>Mugo Pine, 15 gal/B&amp;B</t>
+  </si>
+  <si>
+    <t>Mulch</t>
+  </si>
+  <si>
+    <t>Mulch, Shredded Cedar, Bagged</t>
+  </si>
+  <si>
+    <t>Mulch, Shredded Cedar, Bulk</t>
+  </si>
+  <si>
+    <t>Mulch, Soil Pep, Bagged</t>
+  </si>
+  <si>
+    <t>Mulch, Soil Pep, Bulk</t>
+  </si>
+  <si>
+    <t>NDS drain box, 12" Includes Grate and Inserts</t>
+  </si>
+  <si>
+    <t>NDS Drain Box, 9" Includes Grate and Inserts</t>
+  </si>
+  <si>
+    <t>Neem Oil, bottle</t>
+  </si>
+  <si>
+    <t>Netafim</t>
+  </si>
+  <si>
+    <t>Node, 1 Station</t>
+  </si>
+  <si>
+    <t>Node, 2 Station</t>
+  </si>
+  <si>
+    <t>Noxious weed control</t>
+  </si>
+  <si>
+    <t>Nozzle, MP Rotator</t>
+  </si>
+  <si>
+    <t>Nozzle, RVAN</t>
+  </si>
+  <si>
+    <t>Paver Edge, ft</t>
+  </si>
+  <si>
+    <t>Paver, 2-3"</t>
+  </si>
+  <si>
+    <t>Peony cages, new</t>
+  </si>
+  <si>
+    <t>Per Diem</t>
+  </si>
+  <si>
+    <t>Per Diem, daily</t>
+  </si>
+  <si>
+    <t>Per Diem, overnight</t>
+  </si>
+  <si>
+    <t>Perennials</t>
+  </si>
+  <si>
+    <t>Perennial, 1 gal</t>
+  </si>
+  <si>
+    <t>Perennial, 2 gal</t>
+  </si>
+  <si>
+    <t>Perennial, 4"</t>
+  </si>
+  <si>
+    <t>Perennial, Peony</t>
+  </si>
+  <si>
+    <t>perennial, Qt</t>
+  </si>
+  <si>
+    <t>Perennial, Woody 1 gal (Kinnick, Mahonia, Rabbitbrush)</t>
+  </si>
+  <si>
+    <t>Pine, Austrian/Scotch/Ponderosa, 10'</t>
+  </si>
+  <si>
+    <t>Pine, Austrian/Scotch/Ponderosa, 12'</t>
+  </si>
+  <si>
+    <t>Pine, Austrian/Scotch/Ponderosa, 6'</t>
+  </si>
+  <si>
+    <t>Pine, Austrian/Scotch/Ponderosa, 8'</t>
+  </si>
+  <si>
+    <t>Plant, Misc</t>
+  </si>
+  <si>
+    <t>Plants, Shrub, Miscellaneous</t>
+  </si>
+  <si>
+    <t>Poly Slip Fix</t>
+  </si>
+  <si>
+    <t>Potting soil, bag</t>
+  </si>
+  <si>
+    <t>Rain Sensor</t>
+  </si>
+  <si>
+    <t>Rainbird ESP-SM3 module</t>
+  </si>
+  <si>
+    <t>Rebar, 1/2"</t>
+  </si>
+  <si>
+    <t>Road Mix, (1" or 3")</t>
+  </si>
+  <si>
+    <t>Root Start</t>
+  </si>
+  <si>
+    <t>Roundup</t>
+  </si>
+  <si>
+    <t>Scree, Flatwillow</t>
+  </si>
+  <si>
+    <t>Seed Mix, Lawn</t>
+  </si>
+  <si>
+    <t>Seed Mix, Native</t>
+  </si>
+  <si>
+    <t>Shrub, Deciduous 15 gal/B&amp;B</t>
+  </si>
+  <si>
+    <t>Shrub, Deciduous 2 gal</t>
+  </si>
+  <si>
+    <t>Shrub, Deciduous 5 gal</t>
+  </si>
+  <si>
+    <t>Shrub, Deciduous 7 gal</t>
+  </si>
+  <si>
+    <t>Shrub, Evergreen 15 gal/B&amp;B</t>
+  </si>
+  <si>
+    <t>Shrub, Evergreen 2 gal</t>
+  </si>
+  <si>
+    <t>Shrub, Evergreen 5 gal</t>
+  </si>
+  <si>
+    <t>Shrub, Evergreen 7/10 gal</t>
+  </si>
+  <si>
+    <t>Shrub, Multistem, 6-8'</t>
+  </si>
+  <si>
+    <t>Spaghetti Pipe</t>
+  </si>
+  <si>
+    <t>Sprinkler, 1804</t>
+  </si>
+  <si>
+    <t>Sprinkler, 1812</t>
+  </si>
+  <si>
+    <t>Sprinkler, 3504</t>
+  </si>
+  <si>
+    <t>Sprinkler, 5012</t>
+  </si>
+  <si>
+    <t>Sprinkler, Rainbird 3500</t>
+  </si>
+  <si>
+    <t>Spruce, 10'</t>
+  </si>
+  <si>
+    <t>Spruce, 12'</t>
+  </si>
+  <si>
+    <t>Spruce, 14'</t>
+  </si>
+  <si>
+    <t>Spruce, 16'</t>
+  </si>
+  <si>
+    <t>Spruce, 18'</t>
+  </si>
+  <si>
+    <t>Spruce, 20'</t>
+  </si>
+  <si>
+    <t>Spruce, 22'</t>
+  </si>
+  <si>
+    <t>Spruce, 4'</t>
+  </si>
+  <si>
+    <t>Spruce, 6'</t>
+  </si>
+  <si>
+    <t>Spruce, 8'</t>
+  </si>
+  <si>
+    <t>Stone, Rock bark or Equivalent</t>
+  </si>
+  <si>
+    <t>Swing Fittings</t>
+  </si>
+  <si>
+    <t>Swing Pipe</t>
+  </si>
+  <si>
+    <t>T-post, 6' Metal</t>
+  </si>
+  <si>
+    <t>Topsoil</t>
+  </si>
+  <si>
+    <t>Treads, Frontier</t>
+  </si>
+  <si>
+    <t>Twine</t>
+  </si>
+  <si>
+    <t>Weedmat Pins</t>
+  </si>
+  <si>
+    <t>Weedmat</t>
+  </si>
+  <si>
+    <t>Wildflower Seed</t>
+  </si>
+  <si>
+    <t>Wire Nuts, 3M (pair)</t>
+  </si>
+  <si>
+    <t>Wire Nuts, Snaplock</t>
+  </si>
+  <si>
+    <t>Wire, 2-wire Irrigation Control</t>
+  </si>
+  <si>
+    <t>Wire, Landscaping Lighting 10 Gauge</t>
+  </si>
+  <si>
+    <t>Wood Tree Post</t>
+  </si>
+  <si>
+    <t>1" Poly Repair Bundle</t>
+  </si>
+  <si>
+    <t>1.25" Poly Repair Bundle</t>
+  </si>
+  <si>
+    <t>1.5" Poly Repair Bundle</t>
+  </si>
+  <si>
+    <t>Wire Splice Bundle (7 Strand)</t>
+  </si>
+  <si>
+    <t>Wire Splice Bundle (10 Strand)</t>
+  </si>
+  <si>
+    <t>Wire Splice Bundle (13 Strand)</t>
+  </si>
+  <si>
+    <t>Option 1 name</t>
+  </si>
+  <si>
+    <t>Option 1 value</t>
+  </si>
+  <si>
+    <t>Option 2 name</t>
+  </si>
+  <si>
+    <t>Option 2 value</t>
+  </si>
+  <si>
+    <t>Option 3 name</t>
+  </si>
+  <si>
+    <t>Option 3 value</t>
+  </si>
+  <si>
+    <t>Option 4 name</t>
+  </si>
+  <si>
+    <t>Option 4 value</t>
+  </si>
+  <si>
+    <t>Option 5 name</t>
+  </si>
+  <si>
+    <t>Option 5 value</t>
+  </si>
+  <si>
+    <t>Install Hourly labor</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>Labor</t>
+  </si>
+  <si>
+    <t>Irrigation Service Call, hourly-BS</t>
+  </si>
+  <si>
+    <t>Irrigation Service Call, hourly-Bzn</t>
+  </si>
+  <si>
+    <t>Irrigation Techinician Hourly labor</t>
+  </si>
+  <si>
+    <t>Irrigation Technician Hourly Labor</t>
+  </si>
+  <si>
+    <t>Maintenance Hourly Labor - BIG SKY</t>
+  </si>
+  <si>
+    <t>Maintenance Hourly Labor - TOWN</t>
+  </si>
+  <si>
+    <t>Mow Hourly Rate - BIG SKY</t>
+  </si>
+  <si>
+    <t>Mow Hourly Rate - TOWN</t>
+  </si>
+  <si>
+    <t>Winterization-Bzn</t>
+  </si>
+  <si>
+    <t>Amp Conveyor Rental/ Week</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>AMP Shooter Truck, hourly</t>
+  </si>
+  <si>
+    <t>AMP Shooter Truck</t>
+  </si>
+  <si>
+    <t>Auger Daily Fee</t>
+  </si>
+  <si>
+    <t>Auger</t>
+  </si>
+  <si>
+    <t>Case Loader Daily Fee</t>
+  </si>
+  <si>
+    <t>Case Loader</t>
+  </si>
+  <si>
+    <t>Concrete Mixer Daily Fee</t>
+  </si>
+  <si>
+    <t>Concrete Mixer</t>
+  </si>
+  <si>
+    <t>Crew Truck Daily Fee For Estimates</t>
+  </si>
+  <si>
+    <t>Demo saw daily fee</t>
+  </si>
+  <si>
+    <t>Dingo Daily Fee</t>
+  </si>
+  <si>
+    <t>Dingo</t>
+  </si>
+  <si>
+    <t>Dump Truck, Hourly</t>
+  </si>
+  <si>
+    <t>Dump Truck</t>
+  </si>
+  <si>
+    <t>Excavator, 20 ton Daily Fee</t>
+  </si>
+  <si>
+    <t>Excavator, 20 ton</t>
+  </si>
+  <si>
+    <t>Excavator-Mini Daily Fee</t>
+  </si>
+  <si>
+    <t>Excavator-Mini</t>
+  </si>
+  <si>
+    <t>Face Trencher Daily Fee</t>
+  </si>
+  <si>
+    <t>Face Trencher</t>
+  </si>
+  <si>
+    <t>Flatbed Trailer Daily Fee</t>
+  </si>
+  <si>
+    <t>Flatbed Trailer</t>
+  </si>
+  <si>
+    <t>Hydroseeder Daily Fee</t>
+  </si>
+  <si>
+    <t>Hydroseeder</t>
+  </si>
+  <si>
+    <t>Jumping jack compactor Daily Fee</t>
+  </si>
+  <si>
+    <t>Jumping jack compactor</t>
+  </si>
+  <si>
+    <t>Landscape Rake Daily Fee</t>
+  </si>
+  <si>
+    <t>Landscape Rake</t>
+  </si>
+  <si>
+    <t>Laser Level Daily Fee</t>
+  </si>
+  <si>
+    <t>Laser Level</t>
+  </si>
+  <si>
+    <t>Micro Excavator Daily Fee</t>
+  </si>
+  <si>
+    <t>Micro Excavator</t>
+  </si>
+  <si>
+    <t>Plate compactor Daily Fee</t>
+  </si>
+  <si>
+    <t>Plate compactor</t>
+  </si>
+  <si>
+    <t>Pneumatic post pounder Daily Fee</t>
+  </si>
+  <si>
+    <t>Pneumatic post pounder</t>
+  </si>
+  <si>
+    <t>Power Washer Daily Fee</t>
+  </si>
+  <si>
+    <t>Power Washer</t>
+  </si>
+  <si>
+    <t>Skid Steer with Seeder Daily Fee</t>
+  </si>
+  <si>
+    <t>Skid Steer with Seeder</t>
+  </si>
+  <si>
+    <t>Soil Screen Daily Fee</t>
+  </si>
+  <si>
+    <t>Soil Screen</t>
+  </si>
+  <si>
+    <t>Tiller Daily Fee</t>
+  </si>
+  <si>
+    <t>Tiller</t>
+  </si>
+  <si>
+    <t>Tracked Skid Steer Daily Fee</t>
+  </si>
+  <si>
+    <t>Tracked Skid Steer</t>
+  </si>
+  <si>
+    <t>Weed whacker</t>
+  </si>
+  <si>
+    <t>Welding Kit Daily Fee</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Part Number (Cell B)</t>
+  </si>
+  <si>
+    <t>Quantity (Cell C)</t>
+  </si>
+  <si>
+    <t>Unit Price (Cell D)</t>
+  </si>
+  <si>
+    <t>Calculated Cost (Cell E)</t>
+  </si>
+  <si>
+    <t>**1'' Poly Repair Bundle**</t>
+  </si>
+  <si>
+    <t>Ft 1'' Poly</t>
+  </si>
+  <si>
+    <t>**1.25" Poly Repair Bundle**</t>
+  </si>
+  <si>
+    <t>1.25" Fittings</t>
+  </si>
+  <si>
+    <t>1.25" Crimp Rings</t>
+  </si>
+  <si>
+    <t>Ft 1.25" Poly</t>
+  </si>
+  <si>
+    <t>**1.5" Poly Repair Bundle**</t>
+  </si>
+  <si>
+    <t>1.5" Fittings</t>
+  </si>
+  <si>
+    <t>1.5" Crimp Rings</t>
+  </si>
+  <si>
+    <t>Ft 1.5" Poly</t>
+  </si>
+  <si>
+    <t>**Wire splice bundle (7 Strand)**</t>
+  </si>
+  <si>
+    <t>Snap Locks</t>
+  </si>
+  <si>
+    <t>Ft. 7 strand wire</t>
+  </si>
+  <si>
+    <t>6" Round Valve box</t>
+  </si>
+  <si>
+    <t>**Wire Splice Bundle (10 Strand)**</t>
+  </si>
+  <si>
+    <t>Ft. 10 Strand wire</t>
+  </si>
+  <si>
+    <t>**Wire Splice Bundle ( 13 Strand)**</t>
+  </si>
+  <si>
+    <t>Ft. 13 Strand wire</t>
+  </si>
+  <si>
+    <t>6" Round Valve Box</t>
+  </si>
+  <si>
+    <t>PLEASE DELETE</t>
+  </si>
+  <si>
+    <t>DO NOT USE</t>
+  </si>
+  <si>
+    <t>Annual Flowers, miscellaneous, ea</t>
+  </si>
+  <si>
+    <t>Bulk, misc</t>
+  </si>
+  <si>
     <t>Deer Spray, Big Sky, ea</t>
   </si>
   <si>
-    <t>NEW007</t>
-  </si>
-  <si>
     <t>Deer Spray, Bozeman, ea</t>
-  </si>
-  <si>
-    <t>NEW008</t>
-  </si>
-  <si>
-    <t>Delivery (Install), Big Sky, ea</t>
-  </si>
-  <si>
-    <t>NEW009</t>
-  </si>
-  <si>
-    <t>Delivery, Big Sky, ea</t>
-  </si>
-  <si>
-    <t>Delivery (Install), Bozeman, ea</t>
-  </si>
-  <si>
-    <t>NEW010</t>
-  </si>
-  <si>
-    <t>Delivery, Bozeman, ea</t>
-  </si>
-  <si>
-    <t>Delivery (Maintenance), Big Sky, ea</t>
-  </si>
-  <si>
-    <t>Delivery (Maintenance), Bozeman, ea</t>
-  </si>
-  <si>
-    <t>Douglas Fir, 10', ea</t>
-  </si>
-  <si>
-    <t>LMN44279462</t>
-  </si>
-  <si>
-    <t>Douglas Fir, 6', ea</t>
-  </si>
-  <si>
-    <t>LMN44279620</t>
-  </si>
-  <si>
-    <t>Douglas Fir, 7', ea</t>
-  </si>
-  <si>
-    <t>LMN44279617</t>
-  </si>
-  <si>
-    <t>Douglas Fir, 8', ea</t>
-  </si>
-  <si>
-    <t>LMN44279455</t>
-  </si>
-  <si>
-    <t>Douglas Fir, 9', ea</t>
-  </si>
-  <si>
-    <t>LMN44279460</t>
-  </si>
-  <si>
-    <t>Drip Emitter, ea</t>
-  </si>
-  <si>
-    <t>LMN40150668</t>
-  </si>
-  <si>
-    <t>Dump Fee Big Sky, ea</t>
-  </si>
-  <si>
-    <t>LMN49034492</t>
-  </si>
-  <si>
-    <t>Debris Dump Fee Big Sky, ea</t>
-  </si>
-  <si>
-    <t>Dump Fee Bozeman, ea</t>
-  </si>
-  <si>
-    <t>NEW011</t>
-  </si>
-  <si>
-    <t>Debris Dump Fee Bozeman, ea</t>
-  </si>
-  <si>
-    <t>Edging, Aluminium, ft</t>
-  </si>
-  <si>
-    <t>LMN40150742</t>
-  </si>
-  <si>
-    <t>Edging, Aluminum Edging Corners, ea</t>
-  </si>
-  <si>
-    <t>LMN45549103</t>
-  </si>
-  <si>
-    <t>Aluminum Edging Corners, ea</t>
-  </si>
-  <si>
-    <t>Edging, Plastic, ea</t>
-  </si>
-  <si>
-    <t>NEW012</t>
-  </si>
-  <si>
-    <t>Edging, Steel 5" x 1/4", ft</t>
-  </si>
-  <si>
-    <t>LMN40150741</t>
-  </si>
-  <si>
-    <t>Edging, Steel 5" x 3/16", ft</t>
-  </si>
-  <si>
-    <t>LMN40150740</t>
-  </si>
-  <si>
-    <t>Erosion Control Blanket, straw, sf</t>
-  </si>
-  <si>
-    <t>LMN40150795</t>
-  </si>
-  <si>
-    <t>Fertilizer, Bagged, ea</t>
-  </si>
-  <si>
-    <t>LMN40150793</t>
-  </si>
-  <si>
-    <t>Fertilizer, Liquid, ea</t>
-  </si>
-  <si>
-    <t>NEW013</t>
-  </si>
-  <si>
-    <t>Fertilizer, Spikes, ea</t>
-  </si>
-  <si>
-    <t>NEW014</t>
-  </si>
-  <si>
-    <t>Filter Fabric, sf</t>
-  </si>
-  <si>
-    <t>LMN40150729</t>
-  </si>
-  <si>
-    <t>Flagstone, Dimensional Bluestone, sf</t>
-  </si>
-  <si>
-    <t>LMN40150713</t>
-  </si>
-  <si>
-    <t>Flagstone, Frontier, ton</t>
-  </si>
-  <si>
-    <t>LMN40150710</t>
-  </si>
-  <si>
-    <t>Flagstone, Mohave, ton</t>
-  </si>
-  <si>
-    <t>LMN40150712</t>
-  </si>
-  <si>
-    <t>Flagstone, Windsor Grey, ton</t>
-  </si>
-  <si>
-    <t>LMN40150711</t>
-  </si>
-  <si>
-    <t>Gravel, 3/4"- 2", yd</t>
-  </si>
-  <si>
-    <t>LMN40150723</t>
-  </si>
-  <si>
-    <t>Stone, 3/4" crushed/2" round sewer, yd</t>
-  </si>
-  <si>
-    <t>Hedge Shearing, hr</t>
-  </si>
-  <si>
-    <t>LMN49073499</t>
-  </si>
-  <si>
-    <t>hr</t>
-  </si>
-  <si>
-    <t>Herbicide, gal</t>
-  </si>
-  <si>
-    <t>LMN48941386</t>
-  </si>
-  <si>
-    <t>gal</t>
-  </si>
-  <si>
-    <t>Hose Bib Irrigation Timer, ea</t>
-  </si>
-  <si>
-    <t>LMN45407580</t>
-  </si>
-  <si>
-    <t>Hydromulch, Flexterra, #50 Bale, ea</t>
-  </si>
-  <si>
-    <t>LMN40150792</t>
-  </si>
-  <si>
-    <t>Hydromulch, Wood or Straw, #50 Bale, ea</t>
-  </si>
-  <si>
-    <t>LMN40150794</t>
-  </si>
-  <si>
-    <t>Insecticidal Soap, ea</t>
-  </si>
-  <si>
-    <t>NEW015</t>
-  </si>
-  <si>
-    <t>Irri-gator GT15 pump</t>
-  </si>
-  <si>
-    <t>LMN43624203</t>
-  </si>
-  <si>
-    <t>Lawn Fertilization/Weed Control, ea</t>
-  </si>
-  <si>
-    <t>NEW017</t>
-  </si>
-  <si>
-    <t>Mileage, ea</t>
-  </si>
-  <si>
-    <t>LMN42434662</t>
-  </si>
-  <si>
-    <t>Miscellaneous, 2M Supply, $</t>
-  </si>
-  <si>
-    <t>LMN40150672</t>
-  </si>
-  <si>
-    <t>Miscellaneous, Bulk Material, $</t>
-  </si>
-  <si>
-    <t>LMN40150736</t>
-  </si>
-  <si>
-    <t>Miscellaneous, Irrigation, $</t>
-  </si>
-  <si>
-    <t>NEW036</t>
-  </si>
-  <si>
-    <t>Irrigation, Misc, $</t>
-  </si>
-  <si>
-    <t>Miscellaneous, Lumber, Kenyon Noble Including Hardware, $</t>
-  </si>
-  <si>
-    <t>LMN40150746</t>
-  </si>
-  <si>
-    <t>Miscellaneous, Midland Supply, $</t>
-  </si>
-  <si>
-    <t>LMN40150671</t>
-  </si>
-  <si>
-    <t>Miscellaneous, Mountain Supply, $</t>
-  </si>
-  <si>
-    <t>LMN40150673</t>
-  </si>
-  <si>
-    <t>Mow/Weed Whack Big Sky, hr</t>
-  </si>
-  <si>
-    <t>LMN49034498</t>
-  </si>
-  <si>
-    <t>Mow/Weed Whack Bozeman, hr</t>
-  </si>
-  <si>
-    <t>LMN49067191</t>
-  </si>
-  <si>
-    <t>Mugo Pine, 15 gal/B&amp;B, ea</t>
-  </si>
-  <si>
-    <t>LMN40150772</t>
-  </si>
-  <si>
-    <t>Mulch Glue, gal</t>
-  </si>
-  <si>
-    <t>LMN49355335</t>
-  </si>
-  <si>
-    <t>Mulch, Shredded Cedar, Bagged, ea</t>
-  </si>
-  <si>
-    <t>LMN40150721</t>
-  </si>
-  <si>
-    <t>Mulch, Shredded Cedar, Bulk, yd</t>
-  </si>
-  <si>
-    <t>LMN40150716</t>
-  </si>
-  <si>
-    <t>Mulch, Soil Pep, Bagged, ea</t>
-  </si>
-  <si>
-    <t>LMN40150717</t>
-  </si>
-  <si>
-    <t>Mulch, Soil Pep, Bulk, yd</t>
-  </si>
-  <si>
-    <t>LMN40150722</t>
-  </si>
-  <si>
-    <t>NDS drain box, 12" Includes Grate and Inserts, ea</t>
-  </si>
-  <si>
-    <t>LMN40150735</t>
-  </si>
-  <si>
-    <t>NDS Drain Box, 9" Includes Grate and Inserts, ea</t>
-  </si>
-  <si>
-    <t>LMN40150734</t>
-  </si>
-  <si>
-    <t>Neem Oil, bottle, ea</t>
-  </si>
-  <si>
-    <t>NEW020</t>
-  </si>
-  <si>
-    <t>Netafim, ft</t>
-  </si>
-  <si>
-    <t>LMN40150664</t>
-  </si>
-  <si>
-    <t>Node, 1 Station, ea</t>
-  </si>
-  <si>
-    <t>LMN40150690</t>
-  </si>
-  <si>
-    <t>Node, 2 Station, ea</t>
-  </si>
-  <si>
-    <t>NEW037</t>
-  </si>
-  <si>
-    <t>Noxious weed control, hr</t>
-  </si>
-  <si>
-    <t>NEW021</t>
-  </si>
-  <si>
-    <t>Nozzle, MP Rotator, ea</t>
-  </si>
-  <si>
-    <t>LMN40150687</t>
-  </si>
-  <si>
-    <t>Nozzle, RVAN, ea</t>
-  </si>
-  <si>
-    <t>NEW038</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Paver Edge</t>
-  </si>
-  <si>
-    <t>LMN46147072</t>
-  </si>
-  <si>
-    <t>Ft</t>
-  </si>
-  <si>
-    <t>Paver, 2-3", sf</t>
-  </si>
-  <si>
-    <t>LMN43641020</t>
-  </si>
-  <si>
-    <t>Peony cages, new, ea</t>
-  </si>
-  <si>
-    <t>NEW022</t>
-  </si>
-  <si>
-    <t>Per Diem, daily, ea</t>
-  </si>
-  <si>
-    <t>NEW023</t>
-  </si>
-  <si>
-    <t>Per Diem, overnight, ea</t>
-  </si>
-  <si>
-    <t>NEW024</t>
-  </si>
-  <si>
-    <t>Perennial, 1 gal, ea</t>
-  </si>
-  <si>
-    <t>LMN40150784</t>
-  </si>
-  <si>
-    <t>Perennial, 2 gal, ea</t>
-  </si>
-  <si>
-    <t>LMN43636223</t>
-  </si>
-  <si>
-    <t>Perennial, 4", ea</t>
-  </si>
-  <si>
-    <t>NEW025</t>
-  </si>
-  <si>
-    <t>Perennial, Peony, ea</t>
-  </si>
-  <si>
-    <t>NEW026</t>
-  </si>
-  <si>
-    <t>Perennial, qt, ea</t>
-  </si>
-  <si>
-    <t>LMN46208579</t>
-  </si>
-  <si>
-    <t>Perennial, Woody 1 gal (Kinnick, Mahonia, Rabbitbrush), ea</t>
-  </si>
-  <si>
-    <t>LMN40150785</t>
-  </si>
-  <si>
-    <t>PGV Valve, ea</t>
-  </si>
-  <si>
-    <t>NEW046</t>
-  </si>
-  <si>
-    <t>PGV Valve</t>
-  </si>
-  <si>
-    <t>Pine, Austrian/Scotch/Ponderosa, 10', ea</t>
-  </si>
-  <si>
-    <t>LMN40150775</t>
-  </si>
-  <si>
-    <t>Pine, Austrian/Scotch/Ponderosa, 12', ea</t>
-  </si>
-  <si>
-    <t>LMN44245325</t>
-  </si>
-  <si>
-    <t>Pine, Austrian/Scotch/Ponderosa, 6', ea</t>
-  </si>
-  <si>
-    <t>LMN40150773</t>
-  </si>
-  <si>
-    <t>Pine, Austrian/Scotch/Ponderosa, 8', ea</t>
-  </si>
-  <si>
-    <t>LMN40150774</t>
-  </si>
-  <si>
-    <t>Plant, Misc, $</t>
-  </si>
-  <si>
-    <t>LMN40150787</t>
-  </si>
-  <si>
-    <t>Plants, Shrub, Miscellaneous, ea</t>
-  </si>
-  <si>
-    <t>NEW027</t>
-  </si>
-  <si>
-    <t>Poly Slip Fix, ea</t>
-  </si>
-  <si>
-    <t>NEW045</t>
-  </si>
-  <si>
-    <t>Potting soil, bag, ea</t>
-  </si>
-  <si>
-    <t>NEW028</t>
-  </si>
-  <si>
-    <t>Preene, bucket, ea</t>
-  </si>
-  <si>
-    <t>NEW049</t>
-  </si>
-  <si>
-    <t>Rain Sensor, ea</t>
-  </si>
-  <si>
-    <t>LMN40150703</t>
-  </si>
-  <si>
-    <t>Rainbird 1806</t>
-  </si>
-  <si>
-    <t>LMN42185596</t>
-  </si>
-  <si>
-    <t>Rainbird ESP-SM3 module</t>
-  </si>
-  <si>
-    <t>LMN44195431</t>
-  </si>
-  <si>
-    <t>Rainbird ESP4ME3</t>
-  </si>
-  <si>
-    <t>LMN44195430</t>
-  </si>
-  <si>
-    <t>Rebar, 1/2", ft</t>
-  </si>
-  <si>
-    <t>LMN40150739</t>
-  </si>
-  <si>
-    <t>Road Mix, (1" or 3"), yd</t>
-  </si>
-  <si>
-    <t>LMN40150727</t>
-  </si>
-  <si>
-    <t>Root Start, gal</t>
-  </si>
-  <si>
-    <t>NEW030</t>
-  </si>
-  <si>
-    <t>Roundup, gal</t>
-  </si>
-  <si>
-    <t>NEW031</t>
-  </si>
-  <si>
-    <t>Scree, Flatwillow, ton</t>
-  </si>
-  <si>
-    <t>LMN40150709</t>
-  </si>
-  <si>
-    <t>Seed Mix, Lawn, lb</t>
-  </si>
-  <si>
-    <t>LMN40150789</t>
-  </si>
-  <si>
-    <t>lb</t>
-  </si>
-  <si>
-    <t>Seed Mix, Native, lb</t>
-  </si>
-  <si>
-    <t>LMN40150790</t>
-  </si>
-  <si>
-    <t>Shrub, Deciduous 15 gal/B&amp;B, ea</t>
-  </si>
-  <si>
-    <t>LMN40150779</t>
-  </si>
-  <si>
-    <t>Shrub, Deciduous 2 gal, ea</t>
-  </si>
-  <si>
-    <t>LMN40150776</t>
-  </si>
-  <si>
-    <t>Shrub, Deciduous 5 gal, ea</t>
-  </si>
-  <si>
-    <t>LMN40150777</t>
-  </si>
-  <si>
-    <t>Shrub, Deciduous 7 gal, ea</t>
-  </si>
-  <si>
-    <t>LMN40150778</t>
-  </si>
-  <si>
-    <t>Shrub, Evergreen 15 gal/B&amp;B, ea</t>
-  </si>
-  <si>
-    <t>LMN40150783</t>
-  </si>
-  <si>
-    <t>Shrub, Evergreen 2 gal, ea</t>
-  </si>
-  <si>
-    <t>LMN40150780</t>
-  </si>
-  <si>
-    <t>Shrub, Evergreen 5 gal, ea</t>
-  </si>
-  <si>
-    <t>LMN40150781</t>
-  </si>
-  <si>
-    <t>Shrub, Evergreen 7/10 gal, ea</t>
-  </si>
-  <si>
-    <t>LMN40150782</t>
-  </si>
-  <si>
-    <t>Shrub, Multistem, 6-8', ea</t>
-  </si>
-  <si>
-    <t>LMN40150786</t>
-  </si>
-  <si>
-    <t>Spaghetti Pipe, ft</t>
-  </si>
-  <si>
-    <t>LMN40150669</t>
-  </si>
-  <si>
-    <t>Sprinkler, 1804, ea</t>
-  </si>
-  <si>
-    <t>NEW041</t>
-  </si>
-  <si>
-    <t>Sprinkler, 1812, ea</t>
-  </si>
-  <si>
-    <t>LMN40150688</t>
-  </si>
-  <si>
-    <t>Sprinkler, 3504, ea</t>
-  </si>
-  <si>
-    <t>LMN45473708</t>
-  </si>
-  <si>
-    <t>Sprinker, 3504, ea</t>
-  </si>
-  <si>
-    <t>Sprinkler, 5012, ea</t>
-  </si>
-  <si>
-    <t>LMN40150689</t>
-  </si>
-  <si>
-    <t>Sprinkler, Rainbird 3500, ea</t>
-  </si>
-  <si>
-    <t>NEW042</t>
-  </si>
-  <si>
-    <t>Spruce, 10', ea</t>
-  </si>
-  <si>
-    <t>LMN40150750</t>
-  </si>
-  <si>
-    <t>Spruce, 12', ea</t>
-  </si>
-  <si>
-    <t>LMN40150751</t>
-  </si>
-  <si>
-    <t>Spruce, 14', ea</t>
-  </si>
-  <si>
-    <t>LMN40150752</t>
-  </si>
-  <si>
-    <t>Spruce, 16', ea</t>
-  </si>
-  <si>
-    <t>LMN40150753</t>
-  </si>
-  <si>
-    <t>Spruce, 18', ea</t>
-  </si>
-  <si>
-    <t>LMN40150754</t>
-  </si>
-  <si>
-    <t>Spruce, 20', ea</t>
-  </si>
-  <si>
-    <t>LMN40150755</t>
-  </si>
-  <si>
-    <t>Spruce, 22', ea</t>
-  </si>
-  <si>
-    <t>LMN40150756</t>
-  </si>
-  <si>
-    <t>Spruce, 4', ea</t>
-  </si>
-  <si>
-    <t>LMN40150749</t>
-  </si>
-  <si>
-    <t>Spruce, 6', ea</t>
-  </si>
-  <si>
-    <t>LMN40150747</t>
-  </si>
-  <si>
-    <t>Spruce, 8', ea</t>
-  </si>
-  <si>
-    <t>LMN40150748</t>
-  </si>
-  <si>
-    <t>Stone, Rock bark or Equivalent, yd</t>
-  </si>
-  <si>
-    <t>LMN40150718</t>
-  </si>
-  <si>
-    <t>Swing Fittings, ea</t>
-  </si>
-  <si>
-    <t>LMN40150682</t>
-  </si>
-  <si>
-    <t>Swing Pipe, ft</t>
-  </si>
-  <si>
-    <t>LMN40150681</t>
-  </si>
-  <si>
-    <t>T-post, 6' Metal, ea</t>
-  </si>
-  <si>
-    <t>LMN40150743</t>
-  </si>
-  <si>
-    <t>Topsoil, yd</t>
-  </si>
-  <si>
-    <t>LMN40150715</t>
-  </si>
-  <si>
-    <t>Treads, Frontier, ton</t>
-  </si>
-  <si>
-    <t>LMN40150714</t>
-  </si>
-  <si>
-    <t>Twine, ft</t>
-  </si>
-  <si>
-    <t>NEW032</t>
-  </si>
-  <si>
-    <t>Valve Box 6" Round, ea</t>
-  </si>
-  <si>
-    <t>NEW051</t>
-  </si>
-  <si>
-    <t>Valve Box, 6'' Round, ea</t>
-  </si>
-  <si>
-    <t>Valve Box, 10" Round, ea</t>
-  </si>
-  <si>
-    <t>LMN40150678</t>
-  </si>
-  <si>
-    <t>Valve Box, 10'' Round, ea</t>
-  </si>
-  <si>
-    <t>Valve Box, Jumbo, ea</t>
-  </si>
-  <si>
-    <t>LMN40150677</t>
-  </si>
-  <si>
-    <t>Valve box, Normal Rectangular</t>
-  </si>
-  <si>
-    <t>NEW050</t>
-  </si>
-  <si>
-    <t>Valve Box, Rectangular, ea</t>
-  </si>
-  <si>
-    <t>Weedmat Pins, ea</t>
-  </si>
-  <si>
-    <t>NEW052</t>
-  </si>
-  <si>
-    <t>Weedmat, sf</t>
-  </si>
-  <si>
-    <t>LMN40150728</t>
-  </si>
-  <si>
-    <t>Wildflower Seed, lb</t>
-  </si>
-  <si>
-    <t>LMN40150791</t>
-  </si>
-  <si>
-    <t>Wire Nuts, 3M (pair), ea</t>
-  </si>
-  <si>
-    <t>LMN40150702</t>
-  </si>
-  <si>
-    <t>Wire Nuts, Snaplock, ea</t>
-  </si>
-  <si>
-    <t>LMN40150701</t>
-  </si>
-  <si>
-    <t>Wire, 2-wire Irrigation Control, ft</t>
-  </si>
-  <si>
-    <t>LMN40150699</t>
-  </si>
-  <si>
-    <t>Wire, Irrigation Control (10 Strand), ft</t>
-  </si>
-  <si>
-    <t>LMN40150698</t>
-  </si>
-  <si>
-    <t>Wire, 10-strand Irrigation Control, ft</t>
-  </si>
-  <si>
-    <t>Wire, Irrigation Control (13 Strand)</t>
-  </si>
-  <si>
-    <t>NEW054</t>
-  </si>
-  <si>
-    <t>Wire,13 Strand Irrigation Control, Ft</t>
-  </si>
-  <si>
-    <t>Wire, Irrigation Control (7 Strand)</t>
-  </si>
-  <si>
-    <t>NEW053</t>
-  </si>
-  <si>
-    <t>Wire, 7 Strand Irrigation Control, Ft</t>
-  </si>
-  <si>
-    <t>Wire, Landscaping Lighting 10 Gauge, ft</t>
-  </si>
-  <si>
-    <t>LMN40150700</t>
-  </si>
-  <si>
-    <t>Wood Tree Post, ea</t>
-  </si>
-  <si>
-    <t>LMN40150745</t>
-  </si>
-  <si>
-    <t>1" Poly Repair Bundle, ea</t>
-  </si>
-  <si>
-    <t>NEW055</t>
-  </si>
-  <si>
-    <t>1.25" Poly Repair Bundle, ea</t>
-  </si>
-  <si>
-    <t>NEW056</t>
-  </si>
-  <si>
-    <t>1.5" Poly Repair Bundle, ea</t>
-  </si>
-  <si>
-    <t>NEW057</t>
-  </si>
-  <si>
-    <t>Wire Splice Bundle (7 Strand), ea</t>
-  </si>
-  <si>
-    <t>NEW058</t>
-  </si>
-  <si>
-    <t>Wire Splice Bundle (10 Strand), ea</t>
-  </si>
-  <si>
-    <t>NEW059</t>
-  </si>
-  <si>
-    <t>Wire Splice Bundle (13 Strand), ea</t>
-  </si>
-  <si>
-    <t>NEW060</t>
-  </si>
-  <si>
-    <t>Product/Service Name</t>
-  </si>
-  <si>
-    <t>Variant Name</t>
-  </si>
-  <si>
-    <t>Quantity on hand</t>
-  </si>
-  <si>
-    <t>Item type</t>
-  </si>
-  <si>
-    <t>Single,parent or variant?</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>Income Account</t>
-  </si>
-  <si>
-    <t>Expense Account</t>
-  </si>
-  <si>
-    <t>Inventory asset account</t>
-  </si>
-  <si>
-    <t>Sales Description</t>
-  </si>
-  <si>
-    <t>Purchase Description</t>
-  </si>
-  <si>
-    <t>Reorder Point</t>
-  </si>
-  <si>
-    <t>Column 1</t>
-  </si>
-  <si>
-    <t>Non-inventory</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
-    <t>Irrigation Materials</t>
-  </si>
-  <si>
-    <t>1.5" Poly Fitting</t>
-  </si>
-  <si>
-    <t>1.5" Poly</t>
-  </si>
-  <si>
-    <t>1.5" Stretch Repair Coupling</t>
-  </si>
-  <si>
-    <t>1.5" Tie-In Assembly</t>
-  </si>
-  <si>
-    <t>1" Drip Valve</t>
-  </si>
-  <si>
-    <t>1" Fitting</t>
-  </si>
-  <si>
-    <t>1" Poly</t>
-  </si>
-  <si>
-    <t>1" Tie-In Assembly</t>
-  </si>
-  <si>
-    <t>1" Valve</t>
-  </si>
-  <si>
-    <t>1/2" Fitting</t>
-  </si>
-  <si>
-    <t>1/2" Poly</t>
-  </si>
-  <si>
-    <t>2" Poly Fitting</t>
-  </si>
-  <si>
-    <t>2" Poly</t>
-  </si>
-  <si>
-    <t>2" PVC Fitting</t>
-  </si>
-  <si>
-    <t>2" Stretch Repair Coupling</t>
-  </si>
-  <si>
-    <t>3/4" Brass Quick Coupler</t>
-  </si>
-  <si>
-    <t>Landscaping Materials</t>
-  </si>
-  <si>
-    <t>Drainage Materials</t>
-  </si>
-  <si>
-    <t>4" Corrugated Drain Pipe</t>
-  </si>
-  <si>
-    <t>4" Corrugated Fitting</t>
-  </si>
-  <si>
-    <t>4" PVC Sewer Fitting</t>
-  </si>
-  <si>
-    <t>4" PVC Sewer Pipe</t>
-  </si>
-  <si>
-    <t>5004 with Street L</t>
-  </si>
-  <si>
-    <t>800M4 Backflow</t>
-  </si>
-  <si>
-    <t>Action Fitting</t>
-  </si>
-  <si>
-    <t>Action Manifold</t>
-  </si>
-  <si>
-    <t>Plants</t>
-  </si>
-  <si>
-    <t>Trees</t>
-  </si>
-  <si>
-    <t>Alpine Fir, 10'</t>
-  </si>
-  <si>
-    <t>Alpine Fir, 12'</t>
-  </si>
-  <si>
-    <t>Annuals</t>
-  </si>
-  <si>
-    <t>Annual Flower Pot, 1 Gal</t>
-  </si>
-  <si>
-    <t>Annual Flower Pot, 1 Qt</t>
-  </si>
-  <si>
-    <t>Annual Flower Pot, 4"</t>
-  </si>
-  <si>
-    <t>Landscape Materials</t>
-  </si>
-  <si>
-    <t>Arbor Tie</t>
-  </si>
-  <si>
-    <t>Aspen, 2.5", Mulit Stem</t>
-  </si>
-  <si>
-    <t>Aspen, 2.5", Single Stem</t>
-  </si>
-  <si>
-    <t>Aspen, 2", Mulit Stem</t>
-  </si>
-  <si>
-    <t>Aspen, 2", Single Stem</t>
-  </si>
-  <si>
-    <t>Aspen, 3.5", Single Stem</t>
-  </si>
-  <si>
-    <t>Aspen, 3", Mulit Stem</t>
-  </si>
-  <si>
-    <t>Aspen, 3", Single Stem</t>
-  </si>
-  <si>
-    <t>Aspen, 4.5", Single Stem</t>
-  </si>
-  <si>
-    <t>Aspen, 4", Single Stem</t>
-  </si>
-  <si>
-    <t>Hardscape Materials</t>
-  </si>
-  <si>
-    <t>Belgard Pavers</t>
-  </si>
-  <si>
-    <t>Blazing Saddles</t>
-  </si>
-  <si>
-    <t>Boulder, Quarry Works</t>
-  </si>
-  <si>
-    <t>Bristlecone Pine, 6'</t>
-  </si>
-  <si>
-    <t>Bubbler</t>
-  </si>
-  <si>
-    <t>Bulbs</t>
-  </si>
-  <si>
-    <t>Bulb</t>
-  </si>
-  <si>
-    <t>Bulk</t>
-  </si>
-  <si>
-    <t>Maintenance</t>
-  </si>
-  <si>
-    <t>Caging, linear</t>
-  </si>
-  <si>
-    <t>Gravel</t>
-  </si>
-  <si>
-    <t>Cobble</t>
-  </si>
-  <si>
-    <t>Landscape Installation</t>
-  </si>
-  <si>
-    <t>Compost, Bagged</t>
-  </si>
-  <si>
-    <t>Compost, Bulk</t>
-  </si>
-  <si>
-    <t>Concrete</t>
-  </si>
-  <si>
-    <t>Concrete Delivered</t>
-  </si>
-  <si>
-    <t>Concrete, Bagged</t>
-  </si>
-  <si>
-    <t>Controller, Hunter HPC 400</t>
-  </si>
-  <si>
-    <t>Controller, Hunter HPC Module</t>
-  </si>
-  <si>
-    <t>Controller, Hunter Icore Dual (2 wire)</t>
-  </si>
-  <si>
-    <t>Controller, Rainbird ESP ME</t>
-  </si>
-  <si>
-    <t>Controller, Rainbird ESP Module</t>
-  </si>
-  <si>
-    <t>Crimp Rings</t>
-  </si>
-  <si>
-    <t>Crusher Fines</t>
-  </si>
-  <si>
-    <t>DC Solenoid</t>
-  </si>
-  <si>
-    <t>Deciduous Cottonwood, 2.5"</t>
-  </si>
-  <si>
-    <t>Deciduous Cottonwood, 2"</t>
-  </si>
-  <si>
-    <t>Deciduous Cottonwood, 3"</t>
-  </si>
-  <si>
-    <t>Deciduous Shade/Fruit, 2.5"</t>
-  </si>
-  <si>
-    <t>Deciduous Shade/Fruit, 2"</t>
-  </si>
-  <si>
-    <t>Deciduous Shade/Fruit, 3"</t>
-  </si>
-  <si>
-    <t>Decoder, Hunter Icore</t>
-  </si>
-  <si>
-    <t>Decomposed Granite</t>
-  </si>
-  <si>
-    <t>Deer Spray</t>
-  </si>
-  <si>
-    <t>Deer Spray, Big Sky</t>
-  </si>
-  <si>
-    <t>Deer Spray, Bozeman</t>
-  </si>
-  <si>
-    <t>Fees</t>
-  </si>
-  <si>
-    <t>Delivery</t>
-  </si>
-  <si>
-    <t>Delivery, Big Sky</t>
-  </si>
-  <si>
-    <t>Delivery, Bozeman</t>
-  </si>
-  <si>
-    <t>Douglas Fir, 10'</t>
-  </si>
-  <si>
-    <t>Douglas Fir, 6'</t>
-  </si>
-  <si>
-    <t>Douglas Fir, 7'</t>
-  </si>
-  <si>
-    <t>Douglas Fir, 8'</t>
-  </si>
-  <si>
-    <t>Douglas Fir, 9'</t>
-  </si>
-  <si>
-    <t>Drip Emitter</t>
-  </si>
-  <si>
-    <t>Dump</t>
-  </si>
-  <si>
-    <t>Edging</t>
-  </si>
-  <si>
-    <t>Edging, Plastic 20', ea</t>
-  </si>
-  <si>
-    <t>Edging, Steel 5"x1/4", ft</t>
-  </si>
-  <si>
-    <t>Seeding</t>
-  </si>
-  <si>
-    <t>Fertilizer</t>
-  </si>
-  <si>
-    <t>Fertilizer, Liquid</t>
-  </si>
-  <si>
-    <t>Fertilizer, Spikes</t>
-  </si>
-  <si>
-    <t>Maintenance:Lawn Care</t>
-  </si>
-  <si>
-    <t>Materials</t>
-  </si>
-  <si>
-    <t>Herbicide</t>
-  </si>
-  <si>
-    <t>Hose Bib Irrigation Timer</t>
-  </si>
-  <si>
-    <t>Hydromulch, Flexterra, #50 Bale</t>
-  </si>
-  <si>
-    <t>Hydromulch, Wood or Straw, #50 Bale</t>
-  </si>
-  <si>
-    <t>Insecticidal Soap</t>
-  </si>
-  <si>
-    <t>Lawn Service, ea</t>
-  </si>
-  <si>
-    <t>Mileage</t>
-  </si>
-  <si>
-    <t>Miscellaneous, 2M Supply</t>
-  </si>
-  <si>
-    <t>Miscellaneous, Bulk Material</t>
-  </si>
-  <si>
-    <t>Miscellaneous, Irrigation</t>
-  </si>
-  <si>
-    <t>Miscellaneous, Lumber, Kenyon Noble Including Hardware</t>
-  </si>
-  <si>
-    <t>Miscellaneous, Midland Supply</t>
-  </si>
-  <si>
-    <t>Miscellaneous, Mountain Supply</t>
-  </si>
-  <si>
-    <t>Shrubs</t>
-  </si>
-  <si>
-    <t>Mugo Pine, 15 gal/B&amp;B</t>
-  </si>
-  <si>
-    <t>Mulch</t>
-  </si>
-  <si>
-    <t>Mulch, Shredded Cedar, Bagged</t>
-  </si>
-  <si>
-    <t>Mulch, Shredded Cedar, Bulk</t>
-  </si>
-  <si>
-    <t>Mulch, Soil Pep, Bagged</t>
-  </si>
-  <si>
-    <t>Mulch, Soil Pep, Bulk</t>
-  </si>
-  <si>
-    <t>NDS drain box, 12" Includes Grate and Inserts</t>
-  </si>
-  <si>
-    <t>NDS Drain Box, 9" Includes Grate and Inserts</t>
-  </si>
-  <si>
-    <t>Neem Oil, bottle</t>
-  </si>
-  <si>
-    <t>Netafim</t>
-  </si>
-  <si>
-    <t>Node, 1 Station</t>
-  </si>
-  <si>
-    <t>Node, 2 Station</t>
-  </si>
-  <si>
-    <t>Noxious weed control</t>
-  </si>
-  <si>
-    <t>Nozzle, MP Rotator</t>
-  </si>
-  <si>
-    <t>Nozzle, RVAN</t>
-  </si>
-  <si>
-    <t>Paver Edge, ft</t>
-  </si>
-  <si>
-    <t>Paver, 2-3"</t>
-  </si>
-  <si>
-    <t>Peony cages, new</t>
-  </si>
-  <si>
-    <t>Per Diem</t>
-  </si>
-  <si>
-    <t>Per Diem, daily</t>
-  </si>
-  <si>
-    <t>Per Diem, overnight</t>
-  </si>
-  <si>
-    <t>Perennials</t>
-  </si>
-  <si>
-    <t>Perennial, 1 gal</t>
-  </si>
-  <si>
-    <t>Perennial, 2 gal</t>
-  </si>
-  <si>
-    <t>Perennial, 4"</t>
-  </si>
-  <si>
-    <t>Perennial, Peony</t>
-  </si>
-  <si>
-    <t>perennial, Qt</t>
-  </si>
-  <si>
-    <t>Perennial, Woody 1 gal (Kinnick, Mahonia, Rabbitbrush)</t>
-  </si>
-  <si>
-    <t>Pine, Austrian/Scotch/Ponderosa, 10'</t>
-  </si>
-  <si>
-    <t>Pine, Austrian/Scotch/Ponderosa, 12'</t>
-  </si>
-  <si>
-    <t>Pine, Austrian/Scotch/Ponderosa, 6'</t>
-  </si>
-  <si>
-    <t>Pine, Austrian/Scotch/Ponderosa, 8'</t>
-  </si>
-  <si>
-    <t>Plant, Misc</t>
-  </si>
-  <si>
-    <t>Plants, Shrub, Miscellaneous</t>
-  </si>
-  <si>
-    <t>Poly Slip Fix</t>
-  </si>
-  <si>
-    <t>Potting soil, bag</t>
-  </si>
-  <si>
-    <t>Rain Sensor</t>
-  </si>
-  <si>
-    <t>Rebar, 1/2"</t>
-  </si>
-  <si>
-    <t>Road Mix, (1" or 3")</t>
-  </si>
-  <si>
-    <t>Root Start</t>
-  </si>
-  <si>
-    <t>Roundup</t>
-  </si>
-  <si>
-    <t>Scree, Flatwillow</t>
-  </si>
-  <si>
-    <t>Seed Mix, Lawn</t>
-  </si>
-  <si>
-    <t>Seed Mix, Native</t>
-  </si>
-  <si>
-    <t>Shrub, Deciduous 15 gal/B&amp;B</t>
-  </si>
-  <si>
-    <t>Shrub, Deciduous 2 gal</t>
-  </si>
-  <si>
-    <t>Shrub, Deciduous 5 gal</t>
-  </si>
-  <si>
-    <t>Shrub, Deciduous 7 gal</t>
-  </si>
-  <si>
-    <t>Shrub, Evergreen 15 gal/B&amp;B</t>
-  </si>
-  <si>
-    <t>Shrub, Evergreen 2 gal</t>
-  </si>
-  <si>
-    <t>Shrub, Evergreen 5 gal</t>
-  </si>
-  <si>
-    <t>Shrub, Evergreen 7/10 gal</t>
-  </si>
-  <si>
-    <t>Shrub, Multistem, 6-8'</t>
-  </si>
-  <si>
-    <t>Spaghetti Pipe</t>
-  </si>
-  <si>
-    <t>Sprinkler, 1804</t>
-  </si>
-  <si>
-    <t>Sprinkler, 1812</t>
-  </si>
-  <si>
-    <t>Sprinkler, 3504</t>
-  </si>
-  <si>
-    <t>Sprinkler, 5012</t>
-  </si>
-  <si>
-    <t>Sprinkler, Rainbird 3500</t>
-  </si>
-  <si>
-    <t>Spruce, 10'</t>
-  </si>
-  <si>
-    <t>Spruce, 12'</t>
-  </si>
-  <si>
-    <t>Spruce, 14'</t>
-  </si>
-  <si>
-    <t>Spruce, 16'</t>
-  </si>
-  <si>
-    <t>Spruce, 18'</t>
-  </si>
-  <si>
-    <t>Spruce, 20'</t>
-  </si>
-  <si>
-    <t>Spruce, 22'</t>
-  </si>
-  <si>
-    <t>Spruce, 4'</t>
-  </si>
-  <si>
-    <t>Spruce, 6'</t>
-  </si>
-  <si>
-    <t>Spruce, 8'</t>
-  </si>
-  <si>
-    <t>Stone, Rock bark or Equivalent</t>
-  </si>
-  <si>
-    <t>Swing Fittings</t>
-  </si>
-  <si>
-    <t>Swing Pipe</t>
-  </si>
-  <si>
-    <t>T-post, 6' Metal</t>
-  </si>
-  <si>
-    <t>Topsoil</t>
-  </si>
-  <si>
-    <t>Treads, Frontier</t>
-  </si>
-  <si>
-    <t>Twine</t>
-  </si>
-  <si>
-    <t>Weedmat Pins</t>
-  </si>
-  <si>
-    <t>Weedmat</t>
-  </si>
-  <si>
-    <t>Wildflower Seed</t>
-  </si>
-  <si>
-    <t>Wire Nuts, 3M (pair)</t>
-  </si>
-  <si>
-    <t>Wire Nuts, Snaplock</t>
-  </si>
-  <si>
-    <t>Wire, 2-wire Irrigation Control</t>
-  </si>
-  <si>
-    <t>Wire, Landscaping Lighting 10 Gauge</t>
-  </si>
-  <si>
-    <t>Wood Tree Post</t>
-  </si>
-  <si>
-    <t>1" Poly Repair Bundle</t>
-  </si>
-  <si>
-    <t>1.25" Poly Repair Bundle</t>
-  </si>
-  <si>
-    <t>1.5" Poly Repair Bundle</t>
-  </si>
-  <si>
-    <t>Wire Splice Bundle (7 Strand)</t>
-  </si>
-  <si>
-    <t>Wire Splice Bundle (10 Strand)</t>
-  </si>
-  <si>
-    <t>Wire Splice Bundle (13 Strand)</t>
-  </si>
-  <si>
-    <t>Option 1 name</t>
-  </si>
-  <si>
-    <t>Option 1 value</t>
-  </si>
-  <si>
-    <t>Option 2 name</t>
-  </si>
-  <si>
-    <t>Option 2 value</t>
-  </si>
-  <si>
-    <t>Option 3 name</t>
-  </si>
-  <si>
-    <t>Option 3 value</t>
-  </si>
-  <si>
-    <t>Option 4 name</t>
-  </si>
-  <si>
-    <t>Option 4 value</t>
-  </si>
-  <si>
-    <t>Option 5 name</t>
-  </si>
-  <si>
-    <t>Option 5 value</t>
-  </si>
-  <si>
-    <t>Install Hourly labor</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>Labor</t>
-  </si>
-  <si>
-    <t>Irrigation Service Call, hourly-BS</t>
-  </si>
-  <si>
-    <t>Irrigation Service Call, hourly-Bzn</t>
-  </si>
-  <si>
-    <t>Irrigation Techinician Hourly labor</t>
-  </si>
-  <si>
-    <t>Irrigation Technician Hourly Labor</t>
-  </si>
-  <si>
-    <t>Maintenance Hourly Labor - BIG SKY</t>
-  </si>
-  <si>
-    <t>Maintenance Hourly Labor - TOWN</t>
-  </si>
-  <si>
-    <t>Mow Hourly Rate - BIG SKY</t>
-  </si>
-  <si>
-    <t>Mow Hourly Rate - TOWN</t>
-  </si>
-  <si>
-    <t>Winterization-Bzn</t>
-  </si>
-  <si>
-    <t>Amp Conveyor Rental/ Week</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>AMP Shooter Truck, hourly</t>
-  </si>
-  <si>
-    <t>AMP Shooter Truck</t>
-  </si>
-  <si>
-    <t>Auger Daily Fee</t>
-  </si>
-  <si>
-    <t>Auger</t>
-  </si>
-  <si>
-    <t>Case Loader Daily Fee</t>
-  </si>
-  <si>
-    <t>Case Loader</t>
-  </si>
-  <si>
-    <t>Concrete Mixer Daily Fee</t>
-  </si>
-  <si>
-    <t>Concrete Mixer</t>
-  </si>
-  <si>
-    <t>Crew Truck Daily Fee For Estimates</t>
-  </si>
-  <si>
-    <t>Demo saw daily fee</t>
-  </si>
-  <si>
-    <t>Dingo Daily Fee</t>
-  </si>
-  <si>
-    <t>Dingo</t>
-  </si>
-  <si>
-    <t>Dump Truck, Hourly</t>
-  </si>
-  <si>
-    <t>Dump Truck</t>
-  </si>
-  <si>
-    <t>Excavator, 20 ton Daily Fee</t>
-  </si>
-  <si>
-    <t>Excavator, 20 ton</t>
-  </si>
-  <si>
-    <t>Excavator-Mini Daily Fee</t>
-  </si>
-  <si>
-    <t>Excavator-Mini</t>
-  </si>
-  <si>
-    <t>Face Trencher Daily Fee</t>
-  </si>
-  <si>
-    <t>Face Trencher</t>
-  </si>
-  <si>
-    <t>Flatbed Trailer Daily Fee</t>
-  </si>
-  <si>
-    <t>Flatbed Trailer</t>
-  </si>
-  <si>
-    <t>Hydroseeder Daily Fee</t>
-  </si>
-  <si>
-    <t>Hydroseeder</t>
-  </si>
-  <si>
-    <t>Jumping jack compactor Daily Fee</t>
-  </si>
-  <si>
-    <t>Jumping jack compactor</t>
-  </si>
-  <si>
-    <t>Landscape Rake Daily Fee</t>
-  </si>
-  <si>
-    <t>Landscape Rake</t>
-  </si>
-  <si>
-    <t>Laser Level Daily Fee</t>
-  </si>
-  <si>
-    <t>Laser Level</t>
-  </si>
-  <si>
-    <t>Micro Excavator Daily Fee</t>
-  </si>
-  <si>
-    <t>Micro Excavator</t>
-  </si>
-  <si>
-    <t>Plate compactor Daily Fee</t>
-  </si>
-  <si>
-    <t>Plate compactor</t>
-  </si>
-  <si>
-    <t>Pneumatic post pounder Daily Fee</t>
-  </si>
-  <si>
-    <t>Pneumatic post pounder</t>
-  </si>
-  <si>
-    <t>Power Washer Daily Fee</t>
-  </si>
-  <si>
-    <t>Power Washer</t>
-  </si>
-  <si>
-    <t>Skid Steer with Seeder Daily Fee</t>
-  </si>
-  <si>
-    <t>Skid Steer with Seeder</t>
-  </si>
-  <si>
-    <t>Soil Screen Daily Fee</t>
-  </si>
-  <si>
-    <t>Soil Screen</t>
-  </si>
-  <si>
-    <t>Tiller Daily Fee</t>
-  </si>
-  <si>
-    <t>Tiller</t>
-  </si>
-  <si>
-    <t>Tracked Skid Steer Daily Fee</t>
-  </si>
-  <si>
-    <t>Tracked Skid Steer</t>
-  </si>
-  <si>
-    <t>Weed whacker</t>
-  </si>
-  <si>
-    <t>Welding Kit Daily Fee</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Part Number (Cell B)</t>
-  </si>
-  <si>
-    <t>Quantity (Cell C)</t>
-  </si>
-  <si>
-    <t>Unit Price (Cell D)</t>
-  </si>
-  <si>
-    <t>Calculated Cost (Cell E)</t>
-  </si>
-  <si>
-    <t>**1'' Poly Repair Bundle**</t>
-  </si>
-  <si>
-    <t>Ft 1'' Poly</t>
-  </si>
-  <si>
-    <t>**1.25" Poly Repair Bundle**</t>
-  </si>
-  <si>
-    <t>1.25" Fittings</t>
-  </si>
-  <si>
-    <t>1.25" Crimp Rings</t>
-  </si>
-  <si>
-    <t>Ft 1.25" Poly</t>
-  </si>
-  <si>
-    <t>**1.5" Poly Repair Bundle**</t>
-  </si>
-  <si>
-    <t>1.5" Fittings</t>
-  </si>
-  <si>
-    <t>1.5" Crimp Rings</t>
-  </si>
-  <si>
-    <t>Ft 1.5" Poly</t>
-  </si>
-  <si>
-    <t>**Wire splice bundle (7 Strand)**</t>
-  </si>
-  <si>
-    <t>Snap Locks</t>
-  </si>
-  <si>
-    <t>Ft. 7 strand wire</t>
-  </si>
-  <si>
-    <t>6" Round Valve box</t>
-  </si>
-  <si>
-    <t>**Wire Splice Bundle (10 Strand)**</t>
-  </si>
-  <si>
-    <t>Ft. 10 Strand wire</t>
-  </si>
-  <si>
-    <t>**Wire Splice Bundle ( 13 Strand)**</t>
-  </si>
-  <si>
-    <t>Ft. 13 Strand wire</t>
-  </si>
-  <si>
-    <t>6" Round Valve Box</t>
-  </si>
-  <si>
-    <t>PLEASE DELETE</t>
-  </si>
-  <si>
-    <t>DO NOT USE</t>
-  </si>
-  <si>
-    <t>Annual Flowers, miscellaneous, ea</t>
-  </si>
-  <si>
-    <t>Bulk, misc</t>
   </si>
   <si>
     <t>Dump fee, ea</t>
@@ -2689,9 +2692,6 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2715,6 +2715,9 @@
     </xf>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -4643,7 +4646,7 @@
         <v>0.0</v>
       </c>
       <c r="I9" s="9">
-        <v>0.0</v>
+        <v>252.5</v>
       </c>
       <c r="J9" s="10">
         <v>504.99</v>
@@ -4971,7 +4974,7 @@
         <v>0.0</v>
       </c>
       <c r="I17" s="9">
-        <v>0.49</v>
+        <v>0.13</v>
       </c>
       <c r="J17" s="10">
         <v>0.49</v>
@@ -5133,7 +5136,7 @@
         <v>0.0</v>
       </c>
       <c r="I21" s="9">
-        <v>0.0</v>
+        <v>4.75</v>
       </c>
       <c r="J21" s="10">
         <v>12.09</v>
@@ -5215,7 +5218,7 @@
         <v>0.0</v>
       </c>
       <c r="I23" s="9">
-        <v>0.0</v>
+        <v>49.75</v>
       </c>
       <c r="J23" s="10">
         <v>97.95</v>
@@ -5494,7 +5497,7 @@
         <v>0.0</v>
       </c>
       <c r="I30" s="9">
-        <v>0.0</v>
+        <v>3.43</v>
       </c>
       <c r="J30" s="10">
         <v>6.59</v>
@@ -5617,7 +5620,9 @@
       <c r="I33" s="9">
         <v>851.5</v>
       </c>
-      <c r="J33" s="15"/>
+      <c r="J33" s="10">
+        <v>1423.29</v>
+      </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
@@ -6226,7 +6231,9 @@
       <c r="I48" s="9">
         <v>7.5</v>
       </c>
-      <c r="J48" s="15"/>
+      <c r="J48" s="10">
+        <v>12.54</v>
+      </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
@@ -6343,7 +6350,9 @@
       <c r="I51" s="9">
         <v>432.0</v>
       </c>
-      <c r="J51" s="15"/>
+      <c r="J51" s="10">
+        <v>722.09</v>
+      </c>
       <c r="K51" s="14"/>
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
@@ -6380,7 +6389,9 @@
       <c r="I52" s="9">
         <v>6.34</v>
       </c>
-      <c r="J52" s="15"/>
+      <c r="J52" s="10">
+        <v>10.6</v>
+      </c>
       <c r="K52" s="14"/>
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
@@ -6698,7 +6709,9 @@
       <c r="I60" s="9">
         <v>7.0</v>
       </c>
-      <c r="J60" s="15"/>
+      <c r="J60" s="10">
+        <v>11.7</v>
+      </c>
       <c r="K60" s="14"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
@@ -6815,7 +6828,7 @@
         <v>0.0</v>
       </c>
       <c r="I63" s="9">
-        <v>0.0</v>
+        <v>1087.03</v>
       </c>
       <c r="J63" s="10">
         <v>2174.7</v>
@@ -6938,7 +6951,7 @@
         <v>0.0</v>
       </c>
       <c r="I66" s="9">
-        <v>0.0</v>
+        <v>0.16</v>
       </c>
       <c r="J66" s="10">
         <v>0.32</v>
@@ -7350,7 +7363,9 @@
       <c r="I76" s="9">
         <v>96.0</v>
       </c>
-      <c r="J76" s="15"/>
+      <c r="J76" s="10">
+        <v>160.47</v>
+      </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c r="M76" s="7"/>
@@ -7613,9 +7628,11 @@
       <c r="I83" s="9">
         <v>825.0</v>
       </c>
-      <c r="J83" s="15"/>
+      <c r="J83" s="10">
+        <v>1379.0</v>
+      </c>
       <c r="K83" s="7"/>
-      <c r="L83" s="16"/>
+      <c r="L83" s="15"/>
       <c r="M83" s="7"/>
       <c r="N83" s="7"/>
       <c r="O83" s="11">
@@ -7650,7 +7667,9 @@
       <c r="I84" s="9">
         <v>345.0</v>
       </c>
-      <c r="J84" s="15"/>
+      <c r="J84" s="10">
+        <v>576.67</v>
+      </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
@@ -7687,7 +7706,9 @@
       <c r="I85" s="9">
         <v>375.0</v>
       </c>
-      <c r="J85" s="15"/>
+      <c r="J85" s="10">
+        <v>626.82</v>
+      </c>
       <c r="K85" s="14"/>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
@@ -7724,7 +7745,9 @@
       <c r="I86" s="9">
         <v>445.0</v>
       </c>
-      <c r="J86" s="15"/>
+      <c r="J86" s="10">
+        <v>743.82</v>
+      </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c r="M86" s="7"/>
@@ -7761,7 +7784,9 @@
       <c r="I87" s="9">
         <v>675.0</v>
       </c>
-      <c r="J87" s="15"/>
+      <c r="J87" s="10">
+        <v>1128.27</v>
+      </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
@@ -7830,7 +7855,9 @@
         <v>19</v>
       </c>
       <c r="H89" s="8"/>
-      <c r="I89" s="9"/>
+      <c r="I89" s="9">
+        <v>35.0</v>
+      </c>
       <c r="J89" s="10">
         <v>55.0</v>
       </c>
@@ -7866,7 +7893,7 @@
         <v>0.0</v>
       </c>
       <c r="I90" s="9">
-        <v>55.0</v>
+        <v>35.0</v>
       </c>
       <c r="J90" s="10">
         <v>55.0</v>
@@ -7913,7 +7940,7 @@
         <v>4.69</v>
       </c>
       <c r="K91" s="14"/>
-      <c r="L91" s="17">
+      <c r="L91" s="16">
         <v>0.31</v>
       </c>
       <c r="M91" s="7"/>
@@ -7950,7 +7977,9 @@
       <c r="I92" s="9">
         <v>12.0</v>
       </c>
-      <c r="J92" s="15"/>
+      <c r="J92" s="10">
+        <v>20.06</v>
+      </c>
       <c r="K92" s="14"/>
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
@@ -8028,7 +8057,9 @@
       <c r="I94" s="9">
         <v>5.04</v>
       </c>
-      <c r="J94" s="15"/>
+      <c r="J94" s="10">
+        <v>8.42</v>
+      </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
@@ -8065,7 +8096,9 @@
       <c r="I95" s="9">
         <v>4.07</v>
       </c>
-      <c r="J95" s="15"/>
+      <c r="J95" s="10">
+        <v>6.8</v>
+      </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
@@ -8305,7 +8338,9 @@
       <c r="I101" s="9">
         <v>12.5</v>
       </c>
-      <c r="J101" s="15"/>
+      <c r="J101" s="10">
+        <v>20.89</v>
+      </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
@@ -8342,7 +8377,7 @@
       <c r="I102" s="9">
         <v>700.0</v>
       </c>
-      <c r="J102" s="18">
+      <c r="J102" s="17">
         <v>805.0</v>
       </c>
       <c r="K102" s="14"/>
@@ -8381,7 +8416,7 @@
       <c r="I103" s="9">
         <v>950.0</v>
       </c>
-      <c r="J103" s="19">
+      <c r="J103" s="18">
         <v>1092.0</v>
       </c>
       <c r="K103" s="14"/>
@@ -8420,7 +8455,7 @@
       <c r="I104" s="9">
         <v>600.0</v>
       </c>
-      <c r="J104" s="18">
+      <c r="J104" s="17">
         <v>690.0</v>
       </c>
       <c r="K104" s="14"/>
@@ -8459,7 +8494,7 @@
       <c r="I105" s="9">
         <v>32.0</v>
       </c>
-      <c r="J105" s="20">
+      <c r="J105" s="19">
         <v>45.0</v>
       </c>
       <c r="K105" s="14"/>
@@ -8562,7 +8597,9 @@
       <c r="I108" s="9">
         <v>40.0</v>
       </c>
-      <c r="J108" s="15"/>
+      <c r="J108" s="10">
+        <v>66.86</v>
+      </c>
       <c r="K108" s="14"/>
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
@@ -8599,9 +8636,11 @@
       <c r="I109" s="9">
         <v>72.0</v>
       </c>
-      <c r="J109" s="15"/>
+      <c r="J109" s="10">
+        <v>120.35</v>
+      </c>
       <c r="K109" s="7"/>
-      <c r="L109" s="16"/>
+      <c r="L109" s="15"/>
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
       <c r="O109" s="11">
@@ -8636,7 +8675,9 @@
       <c r="I110" s="9">
         <v>22.0</v>
       </c>
-      <c r="J110" s="15"/>
+      <c r="J110" s="10">
+        <v>36.77</v>
+      </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
@@ -8710,7 +8751,9 @@
       <c r="I112" s="9">
         <v>619.0</v>
       </c>
-      <c r="J112" s="15"/>
+      <c r="J112" s="10">
+        <v>1034.67</v>
+      </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
@@ -8909,10 +8952,10 @@
         <v>0.0</v>
       </c>
       <c r="I117" s="9">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J117" s="10">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="K117" s="14"/>
       <c r="L117" s="7"/>
@@ -9071,7 +9114,7 @@
         <v>71.0</v>
       </c>
       <c r="K121" s="14"/>
-      <c r="L121" s="17"/>
+      <c r="L121" s="16"/>
       <c r="M121" s="7"/>
       <c r="N121" s="7"/>
       <c r="O121" s="11"/>
@@ -9102,7 +9145,7 @@
         <v>22.0</v>
       </c>
       <c r="K122" s="14"/>
-      <c r="L122" s="17"/>
+      <c r="L122" s="16"/>
       <c r="M122" s="7"/>
       <c r="N122" s="7"/>
       <c r="O122" s="11"/>
@@ -9135,9 +9178,11 @@
       <c r="I123" s="9">
         <v>300.0</v>
       </c>
-      <c r="J123" s="15"/>
+      <c r="J123" s="10">
+        <v>501.45</v>
+      </c>
       <c r="K123" s="14"/>
-      <c r="L123" s="17">
+      <c r="L123" s="16">
         <v>0.29</v>
       </c>
       <c r="M123" s="7"/>
@@ -9365,7 +9410,9 @@
       <c r="I129" s="9">
         <v>85.51</v>
       </c>
-      <c r="J129" s="15"/>
+      <c r="J129" s="10">
+        <v>142.93</v>
+      </c>
       <c r="K129" s="14"/>
       <c r="L129" s="7"/>
       <c r="M129" s="7"/>
@@ -9402,7 +9449,9 @@
       <c r="I130" s="9">
         <v>59.35</v>
       </c>
-      <c r="J130" s="15"/>
+      <c r="J130" s="10">
+        <v>99.2</v>
+      </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
@@ -9448,7 +9497,7 @@
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
       <c r="N131" s="7"/>
-      <c r="O131" s="21">
+      <c r="O131" s="20">
         <v>46129.0</v>
       </c>
       <c r="P131" s="12">
@@ -9641,10 +9690,10 @@
       <c r="H136" s="8">
         <v>0.0</v>
       </c>
-      <c r="I136" s="22">
+      <c r="I136" s="21">
         <v>4.29</v>
       </c>
-      <c r="J136" s="19">
+      <c r="J136" s="18">
         <v>8.59</v>
       </c>
       <c r="K136" s="6" t="s">
@@ -9682,10 +9731,10 @@
       <c r="H137" s="8">
         <v>0.0</v>
       </c>
-      <c r="I137" s="23">
+      <c r="I137" s="22">
         <v>4.29</v>
       </c>
-      <c r="J137" s="18">
+      <c r="J137" s="17">
         <v>8.59</v>
       </c>
       <c r="K137" s="14"/>
@@ -9716,12 +9765,12 @@
       </c>
       <c r="H138" s="8"/>
       <c r="I138" s="9"/>
-      <c r="J138" s="15"/>
+      <c r="J138" s="23"/>
       <c r="K138" s="14"/>
       <c r="L138" s="7"/>
       <c r="M138" s="7"/>
       <c r="N138" s="7"/>
-      <c r="O138" s="21">
+      <c r="O138" s="20">
         <v>46136.0</v>
       </c>
       <c r="P138" s="12">
@@ -9751,7 +9800,9 @@
       <c r="I139" s="9">
         <v>4.88</v>
       </c>
-      <c r="J139" s="15"/>
+      <c r="J139" s="10">
+        <v>8.15</v>
+      </c>
       <c r="K139" s="14"/>
       <c r="L139" s="7"/>
       <c r="M139" s="7"/>
@@ -9788,7 +9839,9 @@
       <c r="I140" s="9">
         <v>7.0</v>
       </c>
-      <c r="J140" s="15"/>
+      <c r="J140" s="10">
+        <v>11.7</v>
+      </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c r="M140" s="7"/>
@@ -9863,10 +9916,10 @@
       <c r="H142" s="8">
         <v>0.0</v>
       </c>
-      <c r="I142" s="22">
+      <c r="I142" s="21">
         <v>68.0</v>
       </c>
-      <c r="J142" s="19">
+      <c r="J142" s="18">
         <v>68.0</v>
       </c>
       <c r="K142" s="6" t="s">
@@ -9904,10 +9957,10 @@
       <c r="H143" s="8">
         <v>0.0</v>
       </c>
-      <c r="I143" s="23">
+      <c r="I143" s="22">
         <v>178.0</v>
       </c>
-      <c r="J143" s="18">
+      <c r="J143" s="17">
         <v>178.0</v>
       </c>
       <c r="K143" s="6" t="s">
@@ -9945,10 +9998,10 @@
       <c r="H144" s="8">
         <v>0.0</v>
       </c>
-      <c r="I144" s="22">
+      <c r="I144" s="21">
         <v>9.5</v>
       </c>
-      <c r="J144" s="19">
+      <c r="J144" s="18">
         <v>25.0</v>
       </c>
       <c r="K144" s="14"/>
@@ -9984,7 +10037,7 @@
       <c r="H145" s="8">
         <v>0.0</v>
       </c>
-      <c r="I145" s="23">
+      <c r="I145" s="22">
         <v>24.0</v>
       </c>
       <c r="J145" s="10">
@@ -10023,7 +10076,7 @@
       <c r="H146" s="8">
         <v>0.0</v>
       </c>
-      <c r="I146" s="22">
+      <c r="I146" s="21">
         <v>8.0</v>
       </c>
       <c r="J146" s="10">
@@ -10064,7 +10117,7 @@
       <c r="H147" s="8">
         <v>0.0</v>
       </c>
-      <c r="I147" s="23">
+      <c r="I147" s="22">
         <v>20.0</v>
       </c>
       <c r="J147" s="10">
@@ -10266,7 +10319,9 @@
       <c r="I152" s="9">
         <v>700.0</v>
       </c>
-      <c r="J152" s="15"/>
+      <c r="J152" s="10">
+        <v>1170.06</v>
+      </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
@@ -10385,7 +10440,9 @@
       <c r="I155" s="9">
         <v>1.0</v>
       </c>
-      <c r="J155" s="15"/>
+      <c r="J155" s="10">
+        <v>1.67</v>
+      </c>
       <c r="K155" s="14"/>
       <c r="L155" s="7"/>
       <c r="M155" s="7"/>
@@ -10420,9 +10477,11 @@
         <v>0.0</v>
       </c>
       <c r="I156" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J156" s="15"/>
+        <v>1.0</v>
+      </c>
+      <c r="J156" s="10">
+        <v>1.67</v>
+      </c>
       <c r="K156" s="14"/>
       <c r="L156" s="7"/>
       <c r="M156" s="7"/>
@@ -10465,7 +10524,7 @@
       <c r="K157" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L157" s="16"/>
+      <c r="L157" s="15"/>
       <c r="M157" s="7"/>
       <c r="N157" s="7"/>
       <c r="O157" s="11">
@@ -10506,7 +10565,7 @@
       <c r="K158" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L158" s="16"/>
+      <c r="L158" s="15"/>
       <c r="M158" s="7"/>
       <c r="N158" s="7"/>
       <c r="O158" s="11">
@@ -10541,7 +10600,7 @@
         <v>50.0</v>
       </c>
       <c r="K159" s="6"/>
-      <c r="L159" s="16"/>
+      <c r="L159" s="15"/>
       <c r="M159" s="7"/>
       <c r="N159" s="7"/>
       <c r="O159" s="11"/>
@@ -10580,7 +10639,7 @@
       <c r="K160" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L160" s="16"/>
+      <c r="L160" s="15"/>
       <c r="M160" s="7"/>
       <c r="N160" s="7"/>
       <c r="O160" s="11">
@@ -10606,7 +10665,9 @@
         <v>357</v>
       </c>
       <c r="F161" s="7"/>
-      <c r="G161" s="14"/>
+      <c r="G161" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="H161" s="8">
         <v>0.0</v>
       </c>
@@ -10641,7 +10702,9 @@
         <v>27</v>
       </c>
       <c r="D162" s="7"/>
-      <c r="E162" s="14"/>
+      <c r="E162" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="F162" s="7"/>
       <c r="G162" s="6" t="s">
         <v>19</v>
@@ -10650,9 +10713,11 @@
         <v>0.0</v>
       </c>
       <c r="I162" s="9">
-        <v>38.32</v>
-      </c>
-      <c r="J162" s="15"/>
+        <v>74.31</v>
+      </c>
+      <c r="J162" s="10">
+        <v>148.62</v>
+      </c>
       <c r="K162" s="14"/>
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
@@ -10676,7 +10741,9 @@
         <v>27</v>
       </c>
       <c r="D163" s="7"/>
-      <c r="E163" s="14"/>
+      <c r="E163" s="6" t="s">
+        <v>361</v>
+      </c>
       <c r="F163" s="7"/>
       <c r="G163" s="6" t="s">
         <v>19</v>
@@ -10685,9 +10752,11 @@
         <v>0.0</v>
       </c>
       <c r="I163" s="9">
-        <v>127.12</v>
-      </c>
-      <c r="J163" s="15"/>
+        <v>136.82</v>
+      </c>
+      <c r="J163" s="10">
+        <v>273.65</v>
+      </c>
       <c r="K163" s="14"/>
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
@@ -10765,7 +10834,9 @@
       <c r="I165" s="9">
         <v>24.0</v>
       </c>
-      <c r="J165" s="15"/>
+      <c r="J165" s="10">
+        <v>40.12</v>
+      </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c r="M165" s="7"/>
@@ -11165,9 +11236,11 @@
       <c r="I175" s="9">
         <v>300.0</v>
       </c>
-      <c r="J175" s="15"/>
+      <c r="J175" s="10">
+        <v>501.45</v>
+      </c>
       <c r="K175" s="7"/>
-      <c r="L175" s="17">
+      <c r="L175" s="16">
         <v>0.29</v>
       </c>
       <c r="M175" s="7"/>
@@ -11208,7 +11281,7 @@
         <v>68.53</v>
       </c>
       <c r="K176" s="14"/>
-      <c r="L176" s="17">
+      <c r="L176" s="16">
         <v>0.29</v>
       </c>
       <c r="M176" s="7"/>
@@ -11249,7 +11322,7 @@
         <v>130.38</v>
       </c>
       <c r="K177" s="14"/>
-      <c r="L177" s="17">
+      <c r="L177" s="16">
         <v>0.29</v>
       </c>
       <c r="M177" s="7"/>
@@ -11366,7 +11439,7 @@
         <v>0.0</v>
       </c>
       <c r="I180" s="9">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="J180" s="10">
         <v>0.33</v>
@@ -11407,7 +11480,7 @@
         <v>0.0</v>
       </c>
       <c r="I181" s="9">
-        <v>0.0</v>
+        <v>4.2</v>
       </c>
       <c r="J181" s="10">
         <v>8.59</v>
@@ -11450,7 +11523,7 @@
       <c r="I182" s="9">
         <v>10.13</v>
       </c>
-      <c r="J182" s="18">
+      <c r="J182" s="17">
         <v>20.96</v>
       </c>
       <c r="K182" s="6" t="s">
@@ -11491,7 +11564,7 @@
       <c r="I183" s="9">
         <v>12.44</v>
       </c>
-      <c r="J183" s="19">
+      <c r="J183" s="18">
         <v>24.89</v>
       </c>
       <c r="K183" s="6" t="s">
@@ -11571,7 +11644,7 @@
         <v>0.0</v>
       </c>
       <c r="I185" s="9">
-        <v>0.0</v>
+        <v>14.65</v>
       </c>
       <c r="J185" s="10">
         <v>32.68</v>
@@ -11694,7 +11767,7 @@
         <v>0.0</v>
       </c>
       <c r="I188" s="9">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="J188" s="10">
         <v>1911.6</v>
@@ -11735,7 +11808,7 @@
         <v>0.0</v>
       </c>
       <c r="I189" s="9">
-        <v>0.0</v>
+        <v>960.0</v>
       </c>
       <c r="J189" s="10">
         <v>2655.0</v>
@@ -11776,7 +11849,7 @@
         <v>0.0</v>
       </c>
       <c r="I190" s="9">
-        <v>0.0</v>
+        <v>1080.0</v>
       </c>
       <c r="J190" s="10">
         <v>3310.0</v>
@@ -11817,7 +11890,7 @@
         <v>0.0</v>
       </c>
       <c r="I191" s="9">
-        <v>0.0</v>
+        <v>1200.0</v>
       </c>
       <c r="J191" s="10">
         <v>4186.0</v>
@@ -11858,7 +11931,7 @@
         <v>0.0</v>
       </c>
       <c r="I192" s="9">
-        <v>0.0</v>
+        <v>1320.0</v>
       </c>
       <c r="J192" s="10">
         <v>4974.0</v>
@@ -13116,7 +13189,7 @@
       <c r="I224" s="9"/>
       <c r="J224" s="10"/>
       <c r="K224" s="6"/>
-      <c r="L224" s="16"/>
+      <c r="L224" s="15"/>
       <c r="M224" s="7"/>
       <c r="N224" s="7"/>
       <c r="O224" s="11"/>
@@ -13134,7 +13207,7 @@
       <c r="I225" s="9"/>
       <c r="J225" s="10"/>
       <c r="K225" s="6"/>
-      <c r="L225" s="16"/>
+      <c r="L225" s="15"/>
       <c r="M225" s="7"/>
       <c r="N225" s="7"/>
       <c r="O225" s="11"/>
@@ -13743,7 +13816,7 @@
       </c>
       <c r="I8" s="28">
         <f>VLOOKUP(A8,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>252.5</v>
       </c>
       <c r="J8" s="26" t="s">
         <v>507</v>
@@ -13967,7 +14040,7 @@
       </c>
       <c r="I16" s="28">
         <f>VLOOKUP(A16,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0.49</v>
+        <v>0.13</v>
       </c>
       <c r="J16" s="26" t="s">
         <v>507</v>
@@ -14079,7 +14152,7 @@
       </c>
       <c r="I20" s="28">
         <f>VLOOKUP(A20,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="J20" s="26" t="s">
         <v>507</v>
@@ -14135,7 +14208,7 @@
       </c>
       <c r="I22" s="28">
         <f>VLOOKUP(A22,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>49.75</v>
       </c>
       <c r="J22" s="26" t="s">
         <v>507</v>
@@ -14331,7 +14404,7 @@
       </c>
       <c r="I29" s="28">
         <f>VLOOKUP(A29,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="J29" s="26" t="s">
         <v>507</v>
@@ -14409,7 +14482,7 @@
       <c r="F32" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H32" s="28">
+      <c r="H32" s="27">
         <f>IF(AND(VLOOKUP(A32,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A32,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A32,MasterMaterials!A:J,10,FALSE),ROUND(I32*1.15/0.688,2))</f>
         <v>1423.29</v>
       </c>
@@ -14829,7 +14902,7 @@
       <c r="F47" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="H47" s="28">
+      <c r="H47" s="27">
         <f>IF(AND(VLOOKUP(A47,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A47,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A47,MasterMaterials!A:J,10,FALSE),ROUND(I47*1.15/0.688,2))</f>
         <v>12.54</v>
       </c>
@@ -14913,7 +14986,7 @@
       <c r="F50" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H50" s="28">
+      <c r="H50" s="27">
         <f>IF(AND(VLOOKUP(A50,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A50,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A50,MasterMaterials!A:J,10,FALSE),ROUND(I50*1.15/0.688,2))</f>
         <v>722.09</v>
       </c>
@@ -14941,7 +15014,7 @@
       <c r="F51" s="26" t="s">
         <v>507</v>
       </c>
-      <c r="H51" s="28">
+      <c r="H51" s="27">
         <f>IF(AND(VLOOKUP(A51,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A51,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A51,MasterMaterials!A:J,10,FALSE),ROUND(I51*1.15/0.688,2))</f>
         <v>10.6</v>
       </c>
@@ -15165,7 +15238,7 @@
       <c r="F59" s="26" t="s">
         <v>566</v>
       </c>
-      <c r="H59" s="28">
+      <c r="H59" s="27">
         <f>IF(AND(VLOOKUP(A59,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A59,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A59,MasterMaterials!A:J,10,FALSE),ROUND(I59*1.15/0.688,2))</f>
         <v>11.7</v>
       </c>
@@ -15255,7 +15328,7 @@
       </c>
       <c r="I62" s="28">
         <f>VLOOKUP(A62,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>1087.03</v>
       </c>
       <c r="J62" s="26" t="s">
         <v>507</v>
@@ -15339,7 +15412,7 @@
       </c>
       <c r="I65" s="28">
         <f>VLOOKUP(A65,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="J65" s="26" t="s">
         <v>507</v>
@@ -15613,7 +15686,7 @@
       <c r="F75" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="H75" s="28">
+      <c r="H75" s="27">
         <f>IF(AND(VLOOKUP(A75,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A75,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A75,MasterMaterials!A:J,10,FALSE),ROUND(I75*1.15/0.688,2))</f>
         <v>160.47</v>
       </c>
@@ -15653,7 +15726,7 @@
         <v>588</v>
       </c>
       <c r="M76" s="26" t="s">
-        <v>589</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" ht="22.5" customHeight="1">
@@ -15681,7 +15754,7 @@
         <v>588</v>
       </c>
       <c r="M77" s="26" t="s">
-        <v>590</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" ht="22.5" customHeight="1">
@@ -15695,7 +15768,7 @@
         <v>506</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H78" s="27">
         <f>IF(AND(VLOOKUP(A78,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A78,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A78,MasterMaterials!A:J,10,FALSE),ROUND(I78*1.15/0.688,2))</f>
@@ -15706,10 +15779,10 @@
         <v>650</v>
       </c>
       <c r="J78" s="26" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M78" s="26" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="79" ht="22.5" customHeight="1">
@@ -15723,7 +15796,7 @@
         <v>506</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H79" s="27">
         <f>IF(AND(VLOOKUP(A79,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A79,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A79,MasterMaterials!A:J,10,FALSE),ROUND(I79*1.15/0.688,2))</f>
@@ -15734,10 +15807,10 @@
         <v>250</v>
       </c>
       <c r="J79" s="26" t="s">
+        <v>590</v>
+      </c>
+      <c r="M79" s="26" t="s">
         <v>592</v>
-      </c>
-      <c r="M79" s="26" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
@@ -15753,10 +15826,10 @@
         <v>506</v>
       </c>
       <c r="F80" s="31" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G80" s="30"/>
-      <c r="H80" s="18">
+      <c r="H80" s="17">
         <f>IF(AND(VLOOKUP(A80,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A80,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A80,MasterMaterials!A:J,10,FALSE),ROUND(I80*1.15/0.688,2))</f>
         <v>250</v>
       </c>
@@ -15765,7 +15838,7 @@
         <v/>
       </c>
       <c r="J80" s="31" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="K80" s="30"/>
       <c r="L80" s="30"/>
@@ -15789,10 +15862,10 @@
         <v>506</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G81" s="36"/>
-      <c r="H81" s="19">
+      <c r="H81" s="18">
         <f>IF(AND(VLOOKUP(A81,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A81,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A81,MasterMaterials!A:J,10,FALSE),ROUND(I81*1.15/0.688,2))</f>
         <v>100</v>
       </c>
@@ -15801,7 +15874,7 @@
         <v/>
       </c>
       <c r="J81" s="37" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="K81" s="36"/>
       <c r="L81" s="36"/>
@@ -15825,7 +15898,7 @@
       <c r="F82" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H82" s="28">
+      <c r="H82" s="27">
         <f>IF(AND(VLOOKUP(A82,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A82,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A82,MasterMaterials!A:J,10,FALSE),ROUND(I82*1.15/0.688,2))</f>
         <v>1379</v>
       </c>
@@ -15837,7 +15910,7 @@
         <v>535</v>
       </c>
       <c r="M82" s="26" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="83" ht="22.5" customHeight="1">
@@ -15853,7 +15926,7 @@
       <c r="F83" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H83" s="28">
+      <c r="H83" s="27">
         <f>IF(AND(VLOOKUP(A83,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A83,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A83,MasterMaterials!A:J,10,FALSE),ROUND(I83*1.15/0.688,2))</f>
         <v>576.67</v>
       </c>
@@ -15865,7 +15938,7 @@
         <v>535</v>
       </c>
       <c r="M83" s="26" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
@@ -15881,7 +15954,7 @@
       <c r="F84" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H84" s="28">
+      <c r="H84" s="27">
         <f>IF(AND(VLOOKUP(A84,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A84,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A84,MasterMaterials!A:J,10,FALSE),ROUND(I84*1.15/0.688,2))</f>
         <v>626.82</v>
       </c>
@@ -15893,7 +15966,7 @@
         <v>535</v>
       </c>
       <c r="M84" s="26" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="85" ht="22.5" customHeight="1">
@@ -15909,7 +15982,7 @@
       <c r="F85" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H85" s="28">
+      <c r="H85" s="27">
         <f>IF(AND(VLOOKUP(A85,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A85,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A85,MasterMaterials!A:J,10,FALSE),ROUND(I85*1.15/0.688,2))</f>
         <v>743.82</v>
       </c>
@@ -15921,7 +15994,7 @@
         <v>535</v>
       </c>
       <c r="M85" s="26" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
@@ -15937,7 +16010,7 @@
       <c r="F86" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H86" s="28">
+      <c r="H86" s="27">
         <f>IF(AND(VLOOKUP(A86,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A86,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A86,MasterMaterials!A:J,10,FALSE),ROUND(I86*1.15/0.688,2))</f>
         <v>1128.27</v>
       </c>
@@ -15949,7 +16022,7 @@
         <v>535</v>
       </c>
       <c r="M86" s="26" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="87" ht="22.5" customHeight="1">
@@ -15977,7 +16050,7 @@
         <v>507</v>
       </c>
       <c r="M87" s="26" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
@@ -16000,7 +16073,7 @@
         <v>250.0</v>
       </c>
       <c r="J88" s="26" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="M88" s="26" t="s">
         <v>207</v>
@@ -16025,10 +16098,10 @@
       </c>
       <c r="I89" s="28">
         <f>VLOOKUP(A89,MasterMaterials!A:I,9,FALSE)</f>
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="J89" s="26" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="M89" s="26" t="s">
         <v>210</v>
@@ -16056,7 +16129,7 @@
         <v>2.09</v>
       </c>
       <c r="J90" s="26" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M90" s="26" t="s">
         <v>211</v>
@@ -16075,7 +16148,7 @@
       <c r="F91" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="H91" s="28">
+      <c r="H91" s="27">
         <f>IF(AND(VLOOKUP(A91,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A91,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A91,MasterMaterials!A:J,10,FALSE),ROUND(I91*1.15/0.688,2))</f>
         <v>20.06</v>
       </c>
@@ -16084,7 +16157,7 @@
         <v>12</v>
       </c>
       <c r="J91" s="26" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M91" s="26" t="s">
         <v>213</v>
@@ -16112,10 +16185,10 @@
         <v>14.75</v>
       </c>
       <c r="J92" s="26" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M92" s="26" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="93" ht="22.5" customHeight="1">
@@ -16131,7 +16204,7 @@
       <c r="F93" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="H93" s="28">
+      <c r="H93" s="27">
         <f>IF(AND(VLOOKUP(A93,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A93,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A93,MasterMaterials!A:J,10,FALSE),ROUND(I93*1.15/0.688,2))</f>
         <v>8.42</v>
       </c>
@@ -16140,10 +16213,10 @@
         <v>5.04</v>
       </c>
       <c r="J93" s="26" t="s">
+        <v>600</v>
+      </c>
+      <c r="M93" s="26" t="s">
         <v>602</v>
-      </c>
-      <c r="M93" s="26" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="94" ht="22.5" customHeight="1">
@@ -16159,7 +16232,7 @@
       <c r="F94" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="H94" s="28">
+      <c r="H94" s="27">
         <f>IF(AND(VLOOKUP(A94,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A94,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A94,MasterMaterials!A:J,10,FALSE),ROUND(I94*1.15/0.688,2))</f>
         <v>6.8</v>
       </c>
@@ -16168,7 +16241,7 @@
         <v>4.07</v>
       </c>
       <c r="J94" s="26" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M94" s="26" t="s">
         <v>220</v>
@@ -16196,7 +16269,7 @@
         <v>0.33</v>
       </c>
       <c r="J95" s="26" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="M95" s="26" t="s">
         <v>222</v>
@@ -16224,7 +16297,7 @@
         <v>34.82</v>
       </c>
       <c r="J96" s="26" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="M96" s="26" t="s">
         <v>224</v>
@@ -16252,10 +16325,10 @@
         <v>7</v>
       </c>
       <c r="J97" s="26" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="M97" s="26" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="98" ht="22.5" customHeight="1">
@@ -16280,10 +16353,10 @@
         <v>1.75</v>
       </c>
       <c r="J98" s="26" t="s">
+        <v>604</v>
+      </c>
+      <c r="M98" s="26" t="s">
         <v>606</v>
-      </c>
-      <c r="M98" s="26" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
@@ -16327,7 +16400,7 @@
       <c r="F100" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="H100" s="28">
+      <c r="H100" s="27">
         <f>IF(AND(VLOOKUP(A100,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A100,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A100,MasterMaterials!A:J,10,FALSE),ROUND(I100*1.15/0.688,2))</f>
         <v>20.89</v>
       </c>
@@ -16465,7 +16538,7 @@
         <v>506</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H105" s="27">
         <f>IF(AND(VLOOKUP(A105,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A105,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A105,MasterMaterials!A:J,10,FALSE),ROUND(I105*1.15/0.688,2))</f>
@@ -16476,7 +16549,7 @@
         <v/>
       </c>
       <c r="J105" s="26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M105" s="26" t="s">
         <v>243</v>
@@ -16504,7 +16577,7 @@
         <v/>
       </c>
       <c r="J106" s="26" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M106" s="26" t="s">
         <v>246</v>
@@ -16523,7 +16596,7 @@
       <c r="F107" s="26" t="s">
         <v>507</v>
       </c>
-      <c r="H107" s="28">
+      <c r="H107" s="27">
         <f>IF(AND(VLOOKUP(A107,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A107,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A107,MasterMaterials!A:J,10,FALSE),ROUND(I107*1.15/0.688,2))</f>
         <v>66.86</v>
       </c>
@@ -16535,7 +16608,7 @@
         <v>507</v>
       </c>
       <c r="M107" s="26" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="108" ht="22.5" customHeight="1">
@@ -16551,7 +16624,7 @@
       <c r="F108" s="26" t="s">
         <v>566</v>
       </c>
-      <c r="H108" s="28">
+      <c r="H108" s="27">
         <f>IF(AND(VLOOKUP(A108,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A108,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A108,MasterMaterials!A:J,10,FALSE),ROUND(I108*1.15/0.688,2))</f>
         <v>120.35</v>
       </c>
@@ -16560,10 +16633,10 @@
         <v>72</v>
       </c>
       <c r="J108" s="26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M108" s="26" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="109" ht="22.5" customHeight="1">
@@ -16579,7 +16652,7 @@
       <c r="F109" s="26" t="s">
         <v>566</v>
       </c>
-      <c r="H109" s="28">
+      <c r="H109" s="27">
         <f>IF(AND(VLOOKUP(A109,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A109,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A109,MasterMaterials!A:J,10,FALSE),ROUND(I109*1.15/0.688,2))</f>
         <v>36.77</v>
       </c>
@@ -16588,10 +16661,10 @@
         <v>22</v>
       </c>
       <c r="J109" s="26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M109" s="26" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="110" ht="22.5" customHeight="1">
@@ -16616,10 +16689,10 @@
         <v>19.95</v>
       </c>
       <c r="J110" s="26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M110" s="26" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="111" ht="22.5" customHeight="1">
@@ -16635,7 +16708,7 @@
       <c r="F111" s="26" t="s">
         <v>507</v>
       </c>
-      <c r="H111" s="28">
+      <c r="H111" s="27">
         <f>IF(AND(VLOOKUP(A111,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A111,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A111,MasterMaterials!A:J,10,FALSE),ROUND(I111*1.15/0.688,2))</f>
         <v>1034.67</v>
       </c>
@@ -16661,7 +16734,7 @@
         <v>506</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H112" s="27">
         <f>IF(AND(VLOOKUP(A112,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A112,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A112,MasterMaterials!A:J,10,FALSE),ROUND(I112*1.15/0.688,2))</f>
@@ -16672,10 +16745,10 @@
         <v>71</v>
       </c>
       <c r="J112" s="26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M112" s="26" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="113" ht="22.5" customHeight="1">
@@ -16689,7 +16762,7 @@
         <v>506</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H113" s="27">
         <f>IF(AND(VLOOKUP(A113,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A113,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A113,MasterMaterials!A:J,10,FALSE),ROUND(I113*1.15/0.688,2))</f>
@@ -16700,10 +16773,10 @@
         <v>2.5</v>
       </c>
       <c r="J113" s="26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M113" s="26" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="114" ht="22.5" customHeight="1">
@@ -16731,7 +16804,7 @@
         <v>507</v>
       </c>
       <c r="M114" s="26" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="115" ht="22.5" customHeight="1">
@@ -16756,10 +16829,10 @@
         <v>1</v>
       </c>
       <c r="J115" s="26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M115" s="26" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="116" ht="22.5" customHeight="1">
@@ -16775,19 +16848,19 @@
       <c r="F116" s="26" t="s">
         <v>507</v>
       </c>
-      <c r="H116" s="27">
+      <c r="H116" s="28">
         <f>IF(AND(VLOOKUP(A116,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A116,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A116,MasterMaterials!A:J,10,FALSE),ROUND(I116*1.15/0.688,2))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I116" s="28">
         <f>VLOOKUP(A116,MasterMaterials!A:I,9,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" s="26" t="s">
         <v>507</v>
       </c>
       <c r="M116" s="26" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="117" ht="22.5" customHeight="1">
@@ -16812,10 +16885,10 @@
         <v>1</v>
       </c>
       <c r="J117" s="26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M117" s="26" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="118" ht="22.5" customHeight="1">
@@ -16843,7 +16916,7 @@
         <v>507</v>
       </c>
       <c r="M118" s="26" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="119" ht="22.5" customHeight="1">
@@ -16871,7 +16944,7 @@
         <v>507</v>
       </c>
       <c r="M119" s="26" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="120" ht="22.5" customHeight="1">
@@ -16885,7 +16958,7 @@
         <v>506</v>
       </c>
       <c r="F120" s="26" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H120" s="27">
         <f>IF(AND(VLOOKUP(A120,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A120,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A120,MasterMaterials!A:J,10,FALSE),ROUND(I120*1.15/0.688,2))</f>
@@ -16896,7 +16969,7 @@
         <v/>
       </c>
       <c r="J120" s="26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M120" s="26" t="s">
         <v>276</v>
@@ -16913,7 +16986,7 @@
         <v>506</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H121" s="27">
         <f>IF(AND(VLOOKUP(A121,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A121,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A121,MasterMaterials!A:J,10,FALSE),ROUND(I121*1.15/0.688,2))</f>
@@ -16924,7 +16997,7 @@
         <v/>
       </c>
       <c r="J121" s="26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M121" s="26" t="s">
         <v>278</v>
@@ -16943,7 +17016,7 @@
       <c r="F122" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H122" s="28">
+      <c r="H122" s="27">
         <f>IF(AND(VLOOKUP(A122,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A122,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A122,MasterMaterials!A:J,10,FALSE),ROUND(I122*1.15/0.688,2))</f>
         <v>501.45</v>
       </c>
@@ -16952,10 +17025,10 @@
         <v>300</v>
       </c>
       <c r="J122" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M122" s="26" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="123" ht="22.5" customHeight="1">
@@ -16974,11 +17047,11 @@
         <v>562</v>
       </c>
       <c r="G123" s="36"/>
-      <c r="H123" s="19">
+      <c r="H123" s="18">
         <f>IF(AND(VLOOKUP(A123,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A123,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A123,MasterMaterials!A:J,10,FALSE),ROUND(I123*1.15/0.688,2))</f>
         <v>48.35</v>
       </c>
-      <c r="I123" s="22">
+      <c r="I123" s="21">
         <f>VLOOKUP(A123,MasterMaterials!A:I,9,FALSE)</f>
         <v>38.68</v>
       </c>
@@ -17014,10 +17087,10 @@
         <v>5.44</v>
       </c>
       <c r="J124" s="26" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="M124" s="26" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="125" ht="22.5" customHeight="1">
@@ -17042,10 +17115,10 @@
         <v>40.94</v>
       </c>
       <c r="J125" s="26" t="s">
+        <v>624</v>
+      </c>
+      <c r="M125" s="26" t="s">
         <v>626</v>
-      </c>
-      <c r="M125" s="26" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="126" ht="22.5" customHeight="1">
@@ -17070,10 +17143,10 @@
         <v>4.42</v>
       </c>
       <c r="J126" s="26" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="M126" s="26" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="127" ht="22.5" customHeight="1">
@@ -17098,10 +17171,10 @@
         <v>41.21</v>
       </c>
       <c r="J127" s="26" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="M127" s="26" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="128" ht="22.5" customHeight="1">
@@ -17117,7 +17190,7 @@
       <c r="F128" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="H128" s="28">
+      <c r="H128" s="27">
         <f>IF(AND(VLOOKUP(A128,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A128,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A128,MasterMaterials!A:J,10,FALSE),ROUND(I128*1.15/0.688,2))</f>
         <v>142.93</v>
       </c>
@@ -17129,7 +17202,7 @@
         <v>525</v>
       </c>
       <c r="M128" s="26" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="129" ht="22.5" customHeight="1">
@@ -17145,7 +17218,7 @@
       <c r="F129" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="H129" s="28">
+      <c r="H129" s="27">
         <f>IF(AND(VLOOKUP(A129,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A129,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A129,MasterMaterials!A:J,10,FALSE),ROUND(I129*1.15/0.688,2))</f>
         <v>99.2</v>
       </c>
@@ -17157,7 +17230,7 @@
         <v>525</v>
       </c>
       <c r="M129" s="26" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="130" ht="22.5" customHeight="1">
@@ -17182,10 +17255,10 @@
         <v>42</v>
       </c>
       <c r="J130" s="26" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M130" s="26" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="131" ht="22.5" customHeight="1">
@@ -17213,7 +17286,7 @@
         <v>507</v>
       </c>
       <c r="M131" s="26" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="132" ht="22.5" customHeight="1">
@@ -17241,7 +17314,7 @@
         <v>507</v>
       </c>
       <c r="M132" s="26" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="133" ht="22.5" customHeight="1">
@@ -17269,7 +17342,7 @@
         <v>507</v>
       </c>
       <c r="M133" s="26" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="134" ht="22.5" customHeight="1">
@@ -17294,10 +17367,10 @@
         <v>81</v>
       </c>
       <c r="J134" s="26" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M134" s="26" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="135" ht="22.5" customHeight="1">
@@ -17325,7 +17398,7 @@
         <v>507</v>
       </c>
       <c r="M135" s="26" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="136" ht="22.5" customHeight="1">
@@ -17353,7 +17426,7 @@
         <v>507</v>
       </c>
       <c r="M136" s="26" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="137" ht="22.5" customHeight="1">
@@ -17372,7 +17445,7 @@
         <v>562</v>
       </c>
       <c r="G137" s="36"/>
-      <c r="H137" s="22">
+      <c r="H137" s="21">
         <f>IF(AND(VLOOKUP(A137,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A137,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A137,MasterMaterials!A:J,10,FALSE),ROUND(I137*1.15/0.688,2))</f>
         <v>0</v>
       </c>
@@ -17403,9 +17476,9 @@
       <c r="F138" s="26" t="s">
         <v>566</v>
       </c>
-      <c r="H138" s="28">
+      <c r="H138" s="27">
         <f>IF(AND(VLOOKUP(A138,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A138,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A138,MasterMaterials!A:J,10,FALSE),ROUND(I138*1.15/0.688,2))</f>
-        <v>8.16</v>
+        <v>8.15</v>
       </c>
       <c r="I138" s="28">
         <f>VLOOKUP(A138,MasterMaterials!A:I,9,FALSE)</f>
@@ -17415,7 +17488,7 @@
         <v>553</v>
       </c>
       <c r="M138" s="26" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="139" ht="22.5" customHeight="1">
@@ -17431,7 +17504,7 @@
       <c r="F139" s="26" t="s">
         <v>566</v>
       </c>
-      <c r="H139" s="28">
+      <c r="H139" s="27">
         <f>IF(AND(VLOOKUP(A139,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A139,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A139,MasterMaterials!A:J,10,FALSE),ROUND(I139*1.15/0.688,2))</f>
         <v>11.7</v>
       </c>
@@ -17443,7 +17516,7 @@
         <v>553</v>
       </c>
       <c r="M139" s="26" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="140" ht="22.5" customHeight="1">
@@ -17471,7 +17544,7 @@
         <v>542</v>
       </c>
       <c r="M140" s="26" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="141" ht="22.5" customHeight="1">
@@ -17485,7 +17558,7 @@
         <v>506</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H141" s="27">
         <f>IF(AND(VLOOKUP(A141,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A141,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A141,MasterMaterials!A:J,10,FALSE),ROUND(I141*1.15/0.688,2))</f>
@@ -17496,10 +17569,10 @@
         <v>68</v>
       </c>
       <c r="J141" s="26" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="M141" s="26" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="142" ht="22.5" customHeight="1">
@@ -17513,7 +17586,7 @@
         <v>506</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H142" s="27">
         <f>IF(AND(VLOOKUP(A142,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A142,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A142,MasterMaterials!A:J,10,FALSE),ROUND(I142*1.15/0.688,2))</f>
@@ -17524,10 +17597,10 @@
         <v>178</v>
       </c>
       <c r="J142" s="26" t="s">
+        <v>641</v>
+      </c>
+      <c r="M142" s="26" t="s">
         <v>643</v>
-      </c>
-      <c r="M142" s="26" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="143" ht="22.5" customHeight="1">
@@ -17552,10 +17625,10 @@
         <v>9.5</v>
       </c>
       <c r="J143" s="26" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M143" s="26" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="144" ht="22.5" customHeight="1">
@@ -17580,10 +17653,10 @@
         <v>24</v>
       </c>
       <c r="J144" s="26" t="s">
+        <v>644</v>
+      </c>
+      <c r="M144" s="26" t="s">
         <v>646</v>
-      </c>
-      <c r="M144" s="26" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="145" ht="22.5" customHeight="1">
@@ -17608,10 +17681,10 @@
         <v>8</v>
       </c>
       <c r="J145" s="26" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M145" s="26" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="146" ht="22.5" customHeight="1">
@@ -17636,10 +17709,10 @@
         <v>20</v>
       </c>
       <c r="J146" s="26" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M146" s="26" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="147" ht="22.5" customHeight="1">
@@ -17664,10 +17737,10 @@
         <v>8.36</v>
       </c>
       <c r="J147" s="26" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M147" s="26" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="148" ht="22.5" customHeight="1">
@@ -17692,10 +17765,10 @@
         <v>17</v>
       </c>
       <c r="J148" s="26" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M148" s="26" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="149" ht="22.5" customHeight="1">
@@ -17751,7 +17824,7 @@
         <v>535</v>
       </c>
       <c r="M150" s="26" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="151" ht="22.5" customHeight="1">
@@ -17770,7 +17843,7 @@
         <v>534</v>
       </c>
       <c r="G151" s="43"/>
-      <c r="H151" s="28">
+      <c r="H151" s="27">
         <f>IF(AND(VLOOKUP(A151,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A151,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A151,MasterMaterials!A:J,10,FALSE),ROUND(I151*1.15/0.688,2))</f>
         <v>1170.06</v>
       </c>
@@ -17782,7 +17855,7 @@
         <v>535</v>
       </c>
       <c r="M151" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="152" ht="22.5" customHeight="1">
@@ -17810,7 +17883,7 @@
         <v>535</v>
       </c>
       <c r="M152" s="26" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="153" ht="22.5" customHeight="1">
@@ -17838,7 +17911,7 @@
         <v>535</v>
       </c>
       <c r="M153" s="26" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="154" ht="22.5" customHeight="1">
@@ -17854,7 +17927,7 @@
       <c r="F154" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H154" s="28">
+      <c r="H154" s="27">
         <f>IF(AND(VLOOKUP(A154,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A154,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A154,MasterMaterials!A:J,10,FALSE),ROUND(I154*1.15/0.688,2))</f>
         <v>1.67</v>
       </c>
@@ -17866,7 +17939,7 @@
         <v>534</v>
       </c>
       <c r="M154" s="26" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="155" ht="22.5" customHeight="1">
@@ -17882,19 +17955,19 @@
       <c r="F155" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H155" s="28">
+      <c r="H155" s="27">
         <f>IF(AND(VLOOKUP(A155,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A155,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A155,MasterMaterials!A:J,10,FALSE),ROUND(I155*1.15/0.688,2))</f>
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="I155" s="28">
         <f>VLOOKUP(A155,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J155" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M155" s="26" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="156" ht="22.5" customHeight="1">
@@ -17922,7 +17995,7 @@
         <v>507</v>
       </c>
       <c r="M156" s="26" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="157" ht="22.5" customHeight="1">
@@ -17950,7 +18023,7 @@
         <v>542</v>
       </c>
       <c r="M157" s="26" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="158" ht="22.5" customHeight="1">
@@ -17975,7 +18048,7 @@
         <v>32.9</v>
       </c>
       <c r="J158" s="26" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M158" s="26" t="s">
         <v>353</v>
@@ -18006,7 +18079,7 @@
         <v>507</v>
       </c>
       <c r="M159" s="26" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="160" ht="22.5" customHeight="1">
@@ -18038,7 +18111,7 @@
       </c>
     </row>
     <row r="161" ht="22.5" customHeight="1">
-      <c r="A161" s="26" t="s">
+      <c r="A161" s="6" t="s">
         <v>359</v>
       </c>
       <c r="D161" s="26" t="s">
@@ -18050,19 +18123,19 @@
       <c r="F161" s="26" t="s">
         <v>507</v>
       </c>
-      <c r="H161" s="28">
+      <c r="H161" s="27">
         <f>IF(AND(VLOOKUP(A161,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A161,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A161,MasterMaterials!A:J,10,FALSE),ROUND(I161*1.15/0.688,2))</f>
-        <v>64.05</v>
+        <v>148.62</v>
       </c>
       <c r="I161" s="28">
         <f>VLOOKUP(A161,MasterMaterials!A:I,9,FALSE)</f>
-        <v>38.32</v>
+        <v>74.31</v>
       </c>
       <c r="J161" s="26" t="s">
         <v>507</v>
       </c>
       <c r="M161" s="26" t="s">
-        <v>359</v>
+        <v>660</v>
       </c>
     </row>
     <row r="162" ht="22.5" customHeight="1">
@@ -18078,13 +18151,13 @@
       <c r="F162" s="26" t="s">
         <v>507</v>
       </c>
-      <c r="H162" s="28">
+      <c r="H162" s="27">
         <f>IF(AND(VLOOKUP(A162,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A162,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A162,MasterMaterials!A:J,10,FALSE),ROUND(I162*1.15/0.688,2))</f>
-        <v>212.48</v>
+        <v>273.65</v>
       </c>
       <c r="I162" s="28">
         <f>VLOOKUP(A162,MasterMaterials!A:I,9,FALSE)</f>
-        <v>127.12</v>
+        <v>136.82</v>
       </c>
       <c r="J162" s="26" t="s">
         <v>507</v>
@@ -18115,10 +18188,10 @@
         <v>0.43</v>
       </c>
       <c r="J163" s="26" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M163" s="26" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="164" ht="22.5" customHeight="1">
@@ -18134,7 +18207,7 @@
       <c r="F164" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="H164" s="28">
+      <c r="H164" s="27">
         <f>IF(AND(VLOOKUP(A164,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A164,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A164,MasterMaterials!A:J,10,FALSE),ROUND(I164*1.15/0.688,2))</f>
         <v>40.12</v>
       </c>
@@ -18146,7 +18219,7 @@
         <v>564</v>
       </c>
       <c r="M164" s="26" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="165" ht="22.5" customHeight="1">
@@ -18171,10 +18244,10 @@
         <v>47</v>
       </c>
       <c r="J165" s="26" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="M165" s="26" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="166" ht="22.5" customHeight="1">
@@ -18199,10 +18272,10 @@
         <v>25.97</v>
       </c>
       <c r="J166" s="26" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M166" s="26" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="167" ht="22.5" customHeight="1">
@@ -18230,7 +18303,7 @@
         <v>553</v>
       </c>
       <c r="M167" s="26" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="168" ht="22.5" customHeight="1">
@@ -18255,10 +18328,10 @@
         <v>8</v>
       </c>
       <c r="J168" s="26" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="M168" s="26" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1">
@@ -18283,10 +18356,10 @@
         <v>12</v>
       </c>
       <c r="J169" s="26" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="M169" s="26" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="170" ht="22.5" customHeight="1">
@@ -18311,10 +18384,10 @@
         <v>90</v>
       </c>
       <c r="J170" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M170" s="26" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="171" ht="22.5" customHeight="1">
@@ -18339,10 +18412,10 @@
         <v>25</v>
       </c>
       <c r="J171" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M171" s="26" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="172" ht="22.5" customHeight="1">
@@ -18367,10 +18440,10 @@
         <v>35</v>
       </c>
       <c r="J172" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M172" s="26" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="173" ht="22.5" customHeight="1">
@@ -18395,10 +18468,10 @@
         <v>72</v>
       </c>
       <c r="J173" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M173" s="26" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="174" ht="22.5" customHeight="1">
@@ -18414,7 +18487,7 @@
       <c r="F174" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="H174" s="28">
+      <c r="H174" s="27">
         <f>IF(AND(VLOOKUP(A174,MasterMaterials!A:J,10,FALSE)&lt;&gt;"",VLOOKUP(A174,MasterMaterials!A:J,10,FALSE)&lt;&gt;0),VLOOKUP(A174,MasterMaterials!A:J,10,FALSE),ROUND(I174*1.15/0.688,2))</f>
         <v>501.45</v>
       </c>
@@ -18423,10 +18496,10 @@
         <v>300</v>
       </c>
       <c r="J174" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M174" s="26" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1">
@@ -18451,10 +18524,10 @@
         <v>41</v>
       </c>
       <c r="J175" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M175" s="26" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="176" ht="22.5" customHeight="1">
@@ -18479,10 +18552,10 @@
         <v>78</v>
       </c>
       <c r="J176" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M176" s="26" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="177" ht="22.5" customHeight="1">
@@ -18507,10 +18580,10 @@
         <v>190</v>
       </c>
       <c r="J177" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M177" s="26" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="178" ht="22.5" customHeight="1">
@@ -18535,10 +18608,10 @@
         <v>203</v>
       </c>
       <c r="J178" s="26" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M178" s="26" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="179" ht="22.5" customHeight="1">
@@ -18560,13 +18633,13 @@
       </c>
       <c r="I179" s="28">
         <f>VLOOKUP(A179,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="J179" s="26" t="s">
         <v>507</v>
       </c>
       <c r="M179" s="26" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="180" ht="22.5" customHeight="1">
@@ -18588,13 +18661,13 @@
       </c>
       <c r="I180" s="28">
         <f>VLOOKUP(A180,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J180" s="26" t="s">
         <v>507</v>
       </c>
       <c r="M180" s="26" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="181" ht="22.5" customHeight="1">
@@ -18622,7 +18695,7 @@
         <v>507</v>
       </c>
       <c r="M181" s="26" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="182" ht="22.5" customHeight="1">
@@ -18650,7 +18723,7 @@
         <v>507</v>
       </c>
       <c r="M182" s="26" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="183" ht="22.5" customHeight="1">
@@ -18678,7 +18751,7 @@
         <v>507</v>
       </c>
       <c r="M183" s="26" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="184" ht="22.5" customHeight="1">
@@ -18700,13 +18773,13 @@
       </c>
       <c r="I184" s="28">
         <f>VLOOKUP(A184,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>14.65</v>
       </c>
       <c r="J184" s="26" t="s">
         <v>507</v>
       </c>
       <c r="M184" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="185" ht="22.5" customHeight="1">
@@ -18734,7 +18807,7 @@
         <v>535</v>
       </c>
       <c r="M185" s="26" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="186" ht="22.5" customHeight="1">
@@ -18762,7 +18835,7 @@
         <v>535</v>
       </c>
       <c r="M186" s="26" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="187" ht="22.5" customHeight="1">
@@ -18784,13 +18857,13 @@
       </c>
       <c r="I187" s="28">
         <f>VLOOKUP(A187,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="J187" s="26" t="s">
         <v>535</v>
       </c>
       <c r="M187" s="26" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="188" ht="22.5" customHeight="1">
@@ -18812,13 +18885,13 @@
       </c>
       <c r="I188" s="28">
         <f>VLOOKUP(A188,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="J188" s="26" t="s">
         <v>535</v>
       </c>
       <c r="M188" s="26" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="189" ht="22.5" customHeight="1">
@@ -18840,13 +18913,13 @@
       </c>
       <c r="I189" s="28">
         <f>VLOOKUP(A189,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="J189" s="26" t="s">
         <v>535</v>
       </c>
       <c r="M189" s="26" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="190" ht="22.5" customHeight="1">
@@ -18868,13 +18941,13 @@
       </c>
       <c r="I190" s="28">
         <f>VLOOKUP(A190,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J190" s="26" t="s">
         <v>535</v>
       </c>
       <c r="M190" s="26" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="191" ht="22.5" customHeight="1">
@@ -18896,13 +18969,13 @@
       </c>
       <c r="I191" s="28">
         <f>VLOOKUP(A191,MasterMaterials!A:I,9,FALSE)</f>
-        <v>0</v>
+        <v>1320</v>
       </c>
       <c r="J191" s="26" t="s">
         <v>535</v>
       </c>
       <c r="M191" s="26" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="192" ht="22.5" customHeight="1">
@@ -18930,7 +19003,7 @@
         <v>535</v>
       </c>
       <c r="M192" s="26" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="193" ht="22.5" customHeight="1">
@@ -18958,7 +19031,7 @@
         <v>535</v>
       </c>
       <c r="M193" s="26" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="194" ht="22.5" customHeight="1">
@@ -18986,7 +19059,7 @@
         <v>535</v>
       </c>
       <c r="M194" s="26" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="195" ht="22.5" customHeight="1">
@@ -19014,7 +19087,7 @@
         <v>564</v>
       </c>
       <c r="M195" s="26" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="196" ht="22.5" customHeight="1">
@@ -19042,7 +19115,7 @@
         <v>507</v>
       </c>
       <c r="M196" s="26" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="197" ht="22.5" customHeight="1">
@@ -19070,7 +19143,7 @@
         <v>507</v>
       </c>
       <c r="M197" s="26" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="198" ht="22.5" customHeight="1">
@@ -19098,7 +19171,7 @@
         <v>542</v>
       </c>
       <c r="M198" s="26" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="199" ht="22.5" customHeight="1">
@@ -19126,7 +19199,7 @@
         <v>542</v>
       </c>
       <c r="M199" s="26" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="200" ht="22.5" customHeight="1">
@@ -19154,7 +19227,7 @@
         <v>553</v>
       </c>
       <c r="M200" s="26" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="201" ht="22.5" customHeight="1">
@@ -19182,7 +19255,7 @@
         <v>542</v>
       </c>
       <c r="M201" s="26" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="202" ht="22.5" customHeight="1">
@@ -19322,7 +19395,7 @@
         <v>507</v>
       </c>
       <c r="M206" s="26" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="207" ht="22.5" customHeight="1">
@@ -19350,7 +19423,7 @@
         <v>507</v>
       </c>
       <c r="M207" s="26" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="208" ht="22.5" customHeight="1">
@@ -19378,7 +19451,7 @@
         <v>507</v>
       </c>
       <c r="M208" s="26" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="209" ht="22.5" customHeight="1">
@@ -19406,7 +19479,7 @@
         <v>507</v>
       </c>
       <c r="M209" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="210" ht="22.5" customHeight="1">
@@ -19434,7 +19507,7 @@
         <v>507</v>
       </c>
       <c r="M210" s="26" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="211" ht="22.5" customHeight="1">
@@ -19462,7 +19535,7 @@
         <v>507</v>
       </c>
       <c r="M211" s="26" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="212" ht="22.5" customHeight="1">
@@ -19574,7 +19647,7 @@
         <v>507</v>
       </c>
       <c r="M215" s="26" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="216" ht="22.5" customHeight="1">
@@ -19602,7 +19675,7 @@
         <v>542</v>
       </c>
       <c r="M216" s="26" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="217" ht="22.5" customHeight="1">
@@ -19630,7 +19703,7 @@
         <v>507</v>
       </c>
       <c r="M217" s="6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="218" ht="22.5" customHeight="1">
@@ -19658,7 +19731,7 @@
         <v>507</v>
       </c>
       <c r="M218" s="6" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="219" ht="22.5" customHeight="1">
@@ -19686,7 +19759,7 @@
         <v>507</v>
       </c>
       <c r="M219" s="6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="220" ht="22.5" customHeight="1">
@@ -19714,7 +19787,7 @@
         <v>507</v>
       </c>
       <c r="M220" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="221" ht="22.5" customHeight="1">
@@ -19742,7 +19815,7 @@
         <v>507</v>
       </c>
       <c r="M221" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="222" ht="22.5" customHeight="1">
@@ -19770,7 +19843,7 @@
         <v>507</v>
       </c>
       <c r="M222" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="223" ht="22.5" customHeight="1">
@@ -21737,7 +21810,7 @@
       </c>
       <c r="I8" s="46">
         <f>MasterMaterials!I9</f>
-        <v>0</v>
+        <v>252.5</v>
       </c>
       <c r="J8" s="47">
         <f>MasterMaterials!J9</f>
@@ -22233,7 +22306,7 @@
       </c>
       <c r="I16" s="46">
         <f>MasterMaterials!I17</f>
-        <v>0.49</v>
+        <v>0.13</v>
       </c>
       <c r="J16" s="47">
         <f>MasterMaterials!J17</f>
@@ -22481,7 +22554,7 @@
       </c>
       <c r="I20" s="46">
         <f>MasterMaterials!I21</f>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="J20" s="47">
         <f>MasterMaterials!J21</f>
@@ -22605,7 +22678,7 @@
       </c>
       <c r="I22" s="46">
         <f>MasterMaterials!I23</f>
-        <v>0</v>
+        <v>49.75</v>
       </c>
       <c r="J22" s="47">
         <f>MasterMaterials!J23</f>
@@ -23039,7 +23112,7 @@
       </c>
       <c r="I29" s="46">
         <f>MasterMaterials!I30</f>
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="J29" s="47">
         <f>MasterMaterials!J30</f>
@@ -23227,9 +23300,9 @@
         <f>MasterMaterials!I33</f>
         <v>851.5</v>
       </c>
-      <c r="J32" s="47" t="str">
+      <c r="J32" s="47">
         <f>MasterMaterials!J33</f>
-        <v/>
+        <v>1423.29</v>
       </c>
       <c r="K32" s="45" t="str">
         <f>MasterMaterials!K33</f>
@@ -24157,9 +24230,9 @@
         <f>MasterMaterials!I48</f>
         <v>7.5</v>
       </c>
-      <c r="J47" s="47" t="str">
+      <c r="J47" s="47">
         <f>MasterMaterials!J48</f>
-        <v/>
+        <v>12.54</v>
       </c>
       <c r="K47" s="45" t="str">
         <f>MasterMaterials!K48</f>
@@ -24343,9 +24416,9 @@
         <f>MasterMaterials!I51</f>
         <v>432</v>
       </c>
-      <c r="J50" s="47" t="str">
+      <c r="J50" s="47">
         <f>MasterMaterials!J51</f>
-        <v/>
+        <v>722.09</v>
       </c>
       <c r="K50" s="45" t="str">
         <f>MasterMaterials!K51</f>
@@ -24405,9 +24478,9 @@
         <f>MasterMaterials!I52</f>
         <v>6.34</v>
       </c>
-      <c r="J51" s="47" t="str">
+      <c r="J51" s="47">
         <f>MasterMaterials!J52</f>
-        <v/>
+        <v>10.6</v>
       </c>
       <c r="K51" s="45" t="str">
         <f>MasterMaterials!K52</f>
@@ -24901,9 +24974,9 @@
         <f>MasterMaterials!I60</f>
         <v>7</v>
       </c>
-      <c r="J59" s="47" t="str">
+      <c r="J59" s="47">
         <f>MasterMaterials!J60</f>
-        <v/>
+        <v>11.7</v>
       </c>
       <c r="K59" s="45" t="str">
         <f>MasterMaterials!K60</f>
@@ -25085,7 +25158,7 @@
       </c>
       <c r="I62" s="46">
         <f>MasterMaterials!I63</f>
-        <v>0</v>
+        <v>1087.03</v>
       </c>
       <c r="J62" s="47">
         <f>MasterMaterials!J63</f>
@@ -25271,7 +25344,7 @@
       </c>
       <c r="I65" s="46">
         <f>MasterMaterials!I66</f>
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="J65" s="47">
         <f>MasterMaterials!J66</f>
@@ -25893,9 +25966,9 @@
         <f>MasterMaterials!I76</f>
         <v>96</v>
       </c>
-      <c r="J75" s="47" t="str">
+      <c r="J75" s="47">
         <f>MasterMaterials!J76</f>
-        <v/>
+        <v>160.47</v>
       </c>
       <c r="K75" s="45" t="str">
         <f>MasterMaterials!K76</f>
@@ -25921,7 +25994,7 @@
     <row r="76">
       <c r="A76" s="45" t="str">
         <f>MasterMaterials!A77</f>
-        <v>Deer Spray, Big Sky, ea</v>
+        <v>Deer and Rabbit Spray, Big Sky, ea</v>
       </c>
       <c r="B76" s="45" t="str">
         <f>MasterMaterials!B77</f>
@@ -25937,7 +26010,7 @@
       </c>
       <c r="E76" s="45" t="str">
         <f>MasterMaterials!E77</f>
-        <v>Deer Spray, Big Sky, ea</v>
+        <v>Deer and Rabbit Spray, Big Sky, ea</v>
       </c>
       <c r="F76" s="45" t="str">
         <f>MasterMaterials!F77</f>
@@ -25983,7 +26056,7 @@
     <row r="77">
       <c r="A77" s="45" t="str">
         <f>MasterMaterials!A78</f>
-        <v>Deer Spray, Bozeman, ea</v>
+        <v>Deer and Rabbit Spray, Bozeman, ea</v>
       </c>
       <c r="B77" s="45" t="str">
         <f>MasterMaterials!B78</f>
@@ -25999,7 +26072,7 @@
       </c>
       <c r="E77" s="45" t="str">
         <f>MasterMaterials!E78</f>
-        <v>Deer Spray, Bozeman, ea</v>
+        <v>Deer and Rabbit Spray, Bozeman, ea</v>
       </c>
       <c r="F77" s="45" t="str">
         <f>MasterMaterials!F78</f>
@@ -26203,9 +26276,9 @@
         <f>MasterMaterials!I83</f>
         <v>825</v>
       </c>
-      <c r="J80" s="47" t="str">
+      <c r="J80" s="47">
         <f>MasterMaterials!J83</f>
-        <v/>
+        <v>1379</v>
       </c>
       <c r="K80" s="45" t="str">
         <f>MasterMaterials!K83</f>
@@ -26265,9 +26338,9 @@
         <f>MasterMaterials!I84</f>
         <v>345</v>
       </c>
-      <c r="J81" s="47" t="str">
+      <c r="J81" s="47">
         <f>MasterMaterials!J84</f>
-        <v/>
+        <v>576.67</v>
       </c>
       <c r="K81" s="45" t="str">
         <f>MasterMaterials!K84</f>
@@ -26327,9 +26400,9 @@
         <f>MasterMaterials!I85</f>
         <v>375</v>
       </c>
-      <c r="J82" s="47" t="str">
+      <c r="J82" s="47">
         <f>MasterMaterials!J85</f>
-        <v/>
+        <v>626.82</v>
       </c>
       <c r="K82" s="45" t="str">
         <f>MasterMaterials!K85</f>
@@ -26389,9 +26462,9 @@
         <f>MasterMaterials!I86</f>
         <v>445</v>
       </c>
-      <c r="J83" s="47" t="str">
+      <c r="J83" s="47">
         <f>MasterMaterials!J86</f>
-        <v/>
+        <v>743.82</v>
       </c>
       <c r="K83" s="45" t="str">
         <f>MasterMaterials!K86</f>
@@ -26451,9 +26524,9 @@
         <f>MasterMaterials!I87</f>
         <v>675</v>
       </c>
-      <c r="J84" s="47" t="str">
+      <c r="J84" s="47">
         <f>MasterMaterials!J87</f>
-        <v/>
+        <v>1128.27</v>
       </c>
       <c r="K84" s="45" t="str">
         <f>MasterMaterials!K87</f>
@@ -26571,9 +26644,9 @@
         <f>MasterMaterials!H89</f>
         <v/>
       </c>
-      <c r="I86" s="46" t="str">
+      <c r="I86" s="46">
         <f>MasterMaterials!I89</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="J86" s="47">
         <f>MasterMaterials!J89</f>
@@ -26635,7 +26708,7 @@
       </c>
       <c r="I87" s="46">
         <f>MasterMaterials!I90</f>
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="J87" s="47">
         <f>MasterMaterials!J90</f>
@@ -26761,9 +26834,9 @@
         <f>MasterMaterials!I92</f>
         <v>12</v>
       </c>
-      <c r="J89" s="47" t="str">
+      <c r="J89" s="47">
         <f>MasterMaterials!J92</f>
-        <v/>
+        <v>20.06</v>
       </c>
       <c r="K89" s="45" t="str">
         <f>MasterMaterials!K92</f>
@@ -26885,9 +26958,9 @@
         <f>MasterMaterials!I94</f>
         <v>5.04</v>
       </c>
-      <c r="J91" s="47" t="str">
+      <c r="J91" s="47">
         <f>MasterMaterials!J94</f>
-        <v/>
+        <v>8.42</v>
       </c>
       <c r="K91" s="45" t="str">
         <f>MasterMaterials!K94</f>
@@ -26947,9 +27020,9 @@
         <f>MasterMaterials!I95</f>
         <v>4.07</v>
       </c>
-      <c r="J92" s="47" t="str">
+      <c r="J92" s="47">
         <f>MasterMaterials!J95</f>
-        <v/>
+        <v>6.8</v>
       </c>
       <c r="K92" s="45" t="str">
         <f>MasterMaterials!K95</f>
@@ -27319,9 +27392,9 @@
         <f>MasterMaterials!I101</f>
         <v>12.5</v>
       </c>
-      <c r="J98" s="47" t="str">
+      <c r="J98" s="47">
         <f>MasterMaterials!J101</f>
-        <v/>
+        <v>20.89</v>
       </c>
       <c r="K98" s="45" t="str">
         <f>MasterMaterials!K101</f>
@@ -27753,9 +27826,9 @@
         <f>MasterMaterials!I108</f>
         <v>40</v>
       </c>
-      <c r="J105" s="47" t="str">
+      <c r="J105" s="47">
         <f>MasterMaterials!J108</f>
-        <v/>
+        <v>66.86</v>
       </c>
       <c r="K105" s="45" t="str">
         <f>MasterMaterials!K108</f>
@@ -27815,9 +27888,9 @@
         <f>MasterMaterials!I109</f>
         <v>72</v>
       </c>
-      <c r="J106" s="47" t="str">
+      <c r="J106" s="47">
         <f>MasterMaterials!J109</f>
-        <v/>
+        <v>120.35</v>
       </c>
       <c r="K106" s="45" t="str">
         <f>MasterMaterials!K109</f>
@@ -27877,9 +27950,9 @@
         <f>MasterMaterials!I110</f>
         <v>22</v>
       </c>
-      <c r="J107" s="47" t="str">
+      <c r="J107" s="47">
         <f>MasterMaterials!J110</f>
-        <v/>
+        <v>36.77</v>
       </c>
       <c r="K107" s="45" t="str">
         <f>MasterMaterials!K110</f>
@@ -28001,9 +28074,9 @@
         <f>MasterMaterials!I112</f>
         <v>619</v>
       </c>
-      <c r="J109" s="47" t="str">
+      <c r="J109" s="47">
         <f>MasterMaterials!J112</f>
-        <v/>
+        <v>1034.67</v>
       </c>
       <c r="K109" s="45" t="str">
         <f>MasterMaterials!K112</f>
@@ -28309,11 +28382,11 @@
       </c>
       <c r="I114" s="46">
         <f>MasterMaterials!I117</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114" s="47">
         <f>MasterMaterials!J117</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K114" s="45" t="str">
         <f>MasterMaterials!K117</f>
@@ -28683,9 +28756,9 @@
         <f>MasterMaterials!I123</f>
         <v>300</v>
       </c>
-      <c r="J120" s="47" t="str">
+      <c r="J120" s="47">
         <f>MasterMaterials!J123</f>
-        <v/>
+        <v>501.45</v>
       </c>
       <c r="K120" s="45" t="str">
         <f>MasterMaterials!K123</f>
@@ -28993,9 +29066,9 @@
         <f>MasterMaterials!I129</f>
         <v>85.51</v>
       </c>
-      <c r="J125" s="47" t="str">
+      <c r="J125" s="47">
         <f>MasterMaterials!J129</f>
-        <v/>
+        <v>142.93</v>
       </c>
       <c r="K125" s="45" t="str">
         <f>MasterMaterials!K129</f>
@@ -29055,9 +29128,9 @@
         <f>MasterMaterials!I130</f>
         <v>59.35</v>
       </c>
-      <c r="J126" s="47" t="str">
+      <c r="J126" s="47">
         <f>MasterMaterials!J130</f>
-        <v/>
+        <v>99.2</v>
       </c>
       <c r="K126" s="45" t="str">
         <f>MasterMaterials!K130</f>
@@ -29551,9 +29624,9 @@
         <f>MasterMaterials!I139</f>
         <v>4.88</v>
       </c>
-      <c r="J134" s="47" t="str">
+      <c r="J134" s="47">
         <f>MasterMaterials!J139</f>
-        <v/>
+        <v>8.15</v>
       </c>
       <c r="K134" s="45" t="str">
         <f>MasterMaterials!K139</f>
@@ -29613,9 +29686,9 @@
         <f>MasterMaterials!I140</f>
         <v>7</v>
       </c>
-      <c r="J135" s="47" t="str">
+      <c r="J135" s="47">
         <f>MasterMaterials!J140</f>
-        <v/>
+        <v>11.7</v>
       </c>
       <c r="K135" s="45" t="str">
         <f>MasterMaterials!K140</f>
@@ -30357,9 +30430,9 @@
         <f>MasterMaterials!I152</f>
         <v>700</v>
       </c>
-      <c r="J147" s="47" t="str">
+      <c r="J147" s="47">
         <f>MasterMaterials!J152</f>
-        <v/>
+        <v>1170.06</v>
       </c>
       <c r="K147" s="45" t="str">
         <f>MasterMaterials!K152</f>
@@ -30543,9 +30616,9 @@
         <f>MasterMaterials!I155</f>
         <v>1</v>
       </c>
-      <c r="J150" s="47" t="str">
+      <c r="J150" s="47">
         <f>MasterMaterials!J155</f>
-        <v/>
+        <v>1.67</v>
       </c>
       <c r="K150" s="45" t="str">
         <f>MasterMaterials!K155</f>
@@ -30603,11 +30676,11 @@
       </c>
       <c r="I151" s="46">
         <f>MasterMaterials!I156</f>
-        <v>0</v>
-      </c>
-      <c r="J151" s="47" t="str">
+        <v>1</v>
+      </c>
+      <c r="J151" s="47">
         <f>MasterMaterials!J156</f>
-        <v/>
+        <v>1.67</v>
       </c>
       <c r="K151" s="45" t="str">
         <f>MasterMaterials!K156</f>
@@ -30905,7 +30978,7 @@
       </c>
       <c r="G156" s="45" t="str">
         <f>MasterMaterials!G161</f>
-        <v/>
+        <v>ea</v>
       </c>
       <c r="H156" s="45">
         <f>MasterMaterials!H161</f>
@@ -30943,7 +31016,7 @@
     <row r="157">
       <c r="A157" s="45" t="str">
         <f>MasterMaterials!A162</f>
-        <v>Rainbird ESP-SM3 module</v>
+        <v>Rainbird ESP-SM6 module</v>
       </c>
       <c r="B157" s="45" t="str">
         <f>MasterMaterials!B162</f>
@@ -30959,7 +31032,7 @@
       </c>
       <c r="E157" s="45" t="str">
         <f>MasterMaterials!E162</f>
-        <v/>
+        <v>Rainbird ESP-SM6 module</v>
       </c>
       <c r="F157" s="45" t="str">
         <f>MasterMaterials!F162</f>
@@ -30975,11 +31048,11 @@
       </c>
       <c r="I157" s="46">
         <f>MasterMaterials!I162</f>
-        <v>38.32</v>
-      </c>
-      <c r="J157" s="47" t="str">
+        <v>74.31</v>
+      </c>
+      <c r="J157" s="47">
         <f>MasterMaterials!J162</f>
-        <v/>
+        <v>148.62</v>
       </c>
       <c r="K157" s="45" t="str">
         <f>MasterMaterials!K162</f>
@@ -31021,7 +31094,7 @@
       </c>
       <c r="E158" s="45" t="str">
         <f>MasterMaterials!E163</f>
-        <v/>
+        <v>Rainbird ESP4ME3</v>
       </c>
       <c r="F158" s="45" t="str">
         <f>MasterMaterials!F163</f>
@@ -31037,11 +31110,11 @@
       </c>
       <c r="I158" s="46">
         <f>MasterMaterials!I163</f>
-        <v>127.12</v>
-      </c>
-      <c r="J158" s="47" t="str">
+        <v>136.82</v>
+      </c>
+      <c r="J158" s="47">
         <f>MasterMaterials!J163</f>
-        <v/>
+        <v>273.65</v>
       </c>
       <c r="K158" s="45" t="str">
         <f>MasterMaterials!K163</f>
@@ -31163,9 +31236,9 @@
         <f>MasterMaterials!I165</f>
         <v>24</v>
       </c>
-      <c r="J160" s="47" t="str">
+      <c r="J160" s="47">
         <f>MasterMaterials!J165</f>
-        <v/>
+        <v>40.12</v>
       </c>
       <c r="K160" s="45" t="str">
         <f>MasterMaterials!K165</f>
@@ -31783,9 +31856,9 @@
         <f>MasterMaterials!I175</f>
         <v>300</v>
       </c>
-      <c r="J170" s="47" t="str">
+      <c r="J170" s="47">
         <f>MasterMaterials!J175</f>
-        <v/>
+        <v>501.45</v>
       </c>
       <c r="K170" s="45" t="str">
         <f>MasterMaterials!K175</f>
@@ -32091,7 +32164,7 @@
       </c>
       <c r="I175" s="46">
         <f>MasterMaterials!I180</f>
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="J175" s="47">
         <f>MasterMaterials!J180</f>
@@ -32153,7 +32226,7 @@
       </c>
       <c r="I176" s="46">
         <f>MasterMaterials!I181</f>
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J176" s="47">
         <f>MasterMaterials!J181</f>
@@ -32401,7 +32474,7 @@
       </c>
       <c r="I180" s="46">
         <f>MasterMaterials!I185</f>
-        <v>0</v>
+        <v>14.65</v>
       </c>
       <c r="J180" s="47">
         <f>MasterMaterials!J185</f>
@@ -32587,7 +32660,7 @@
       </c>
       <c r="I183" s="46">
         <f>MasterMaterials!I188</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="J183" s="47">
         <f>MasterMaterials!J188</f>
@@ -32649,7 +32722,7 @@
       </c>
       <c r="I184" s="46">
         <f>MasterMaterials!I189</f>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="J184" s="47">
         <f>MasterMaterials!J189</f>
@@ -32711,7 +32784,7 @@
       </c>
       <c r="I185" s="46">
         <f>MasterMaterials!I190</f>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="J185" s="47">
         <f>MasterMaterials!J190</f>
@@ -32773,7 +32846,7 @@
       </c>
       <c r="I186" s="46">
         <f>MasterMaterials!I191</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J186" s="47">
         <f>MasterMaterials!J191</f>
@@ -32835,7 +32908,7 @@
       </c>
       <c r="I187" s="46">
         <f>MasterMaterials!I192</f>
-        <v>0</v>
+        <v>1320</v>
       </c>
       <c r="J187" s="47">
         <f>MasterMaterials!J192</f>
@@ -35015,34 +35088,34 @@
         <v>497</v>
       </c>
       <c r="H1" s="52" t="s">
+        <v>714</v>
+      </c>
+      <c r="I1" s="52" t="s">
         <v>715</v>
       </c>
-      <c r="I1" s="52" t="s">
+      <c r="J1" s="52" t="s">
         <v>716</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="K1" s="52" t="s">
         <v>717</v>
       </c>
-      <c r="K1" s="52" t="s">
+      <c r="L1" s="52" t="s">
         <v>718</v>
       </c>
-      <c r="L1" s="52" t="s">
+      <c r="M1" s="52" t="s">
         <v>719</v>
       </c>
-      <c r="M1" s="52" t="s">
+      <c r="N1" s="52" t="s">
         <v>720</v>
       </c>
-      <c r="N1" s="52" t="s">
+      <c r="O1" s="52" t="s">
         <v>721</v>
       </c>
-      <c r="O1" s="52" t="s">
+      <c r="P1" s="52" t="s">
         <v>722</v>
       </c>
-      <c r="P1" s="52" t="s">
+      <c r="Q1" s="52" t="s">
         <v>723</v>
-      </c>
-      <c r="Q1" s="52" t="s">
-        <v>724</v>
       </c>
       <c r="R1" s="52" t="s">
         <v>9</v>
@@ -35072,18 +35145,18 @@
     </row>
     <row r="2">
       <c r="A2" s="54" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B2" s="55"/>
       <c r="C2" s="55"/>
       <c r="D2" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E2" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F2" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G2" s="55"/>
       <c r="H2" s="55"/>
@@ -35103,30 +35176,30 @@
         <v>30.75</v>
       </c>
       <c r="T2" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U2" s="55"/>
       <c r="V2" s="55"/>
       <c r="W2" s="54" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="X2" s="55"/>
       <c r="Y2" s="55"/>
     </row>
     <row r="3">
       <c r="A3" s="54" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B3" s="55"/>
       <c r="C3" s="55"/>
       <c r="D3" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E3" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F3" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G3" s="55"/>
       <c r="H3" s="55"/>
@@ -35146,30 +35219,30 @@
         <v>0.0</v>
       </c>
       <c r="T3" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U3" s="55"/>
       <c r="V3" s="55"/>
       <c r="W3" s="54" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="X3" s="55"/>
       <c r="Y3" s="55"/>
     </row>
     <row r="4">
       <c r="A4" s="54" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55"/>
       <c r="D4" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E4" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G4" s="55"/>
       <c r="H4" s="55"/>
@@ -35189,30 +35262,30 @@
         <v>0.0</v>
       </c>
       <c r="T4" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U4" s="55"/>
       <c r="V4" s="55"/>
       <c r="W4" s="54" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="X4" s="55"/>
       <c r="Y4" s="55"/>
     </row>
     <row r="5">
       <c r="A5" s="54" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B5" s="55"/>
       <c r="C5" s="55"/>
       <c r="D5" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E5" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G5" s="55"/>
       <c r="H5" s="55"/>
@@ -35232,30 +35305,30 @@
         <v>60.72</v>
       </c>
       <c r="T5" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U5" s="55"/>
       <c r="V5" s="55"/>
       <c r="W5" s="54" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="X5" s="55"/>
       <c r="Y5" s="55"/>
     </row>
     <row r="6">
       <c r="A6" s="54" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B6" s="55"/>
       <c r="C6" s="55"/>
       <c r="D6" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E6" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G6" s="55"/>
       <c r="H6" s="55"/>
@@ -35275,30 +35348,30 @@
         <v>0.0</v>
       </c>
       <c r="T6" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U6" s="55"/>
       <c r="V6" s="55"/>
       <c r="W6" s="54" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="X6" s="55"/>
       <c r="Y6" s="55"/>
     </row>
     <row r="7">
       <c r="A7" s="54" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B7" s="55"/>
       <c r="C7" s="55"/>
       <c r="D7" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E7" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F7" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G7" s="55"/>
       <c r="H7" s="55"/>
@@ -35318,30 +35391,30 @@
         <v>0.0</v>
       </c>
       <c r="T7" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U7" s="55"/>
       <c r="V7" s="55"/>
       <c r="W7" s="54" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="X7" s="55"/>
       <c r="Y7" s="55"/>
     </row>
     <row r="8">
       <c r="A8" s="54" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B8" s="55"/>
       <c r="C8" s="55"/>
       <c r="D8" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E8" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F8" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G8" s="55"/>
       <c r="H8" s="55"/>
@@ -35361,30 +35434,30 @@
         <v>31.34</v>
       </c>
       <c r="T8" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U8" s="55"/>
       <c r="V8" s="55"/>
       <c r="W8" s="54" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="X8" s="55"/>
       <c r="Y8" s="55"/>
     </row>
     <row r="9">
       <c r="A9" s="54" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B9" s="55"/>
       <c r="C9" s="55"/>
       <c r="D9" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E9" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G9" s="55"/>
       <c r="H9" s="55"/>
@@ -35404,30 +35477,30 @@
         <v>0.0</v>
       </c>
       <c r="T9" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U9" s="55"/>
       <c r="V9" s="55"/>
       <c r="W9" s="54" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="X9" s="55"/>
       <c r="Y9" s="55"/>
     </row>
     <row r="10">
       <c r="A10" s="54" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B10" s="55"/>
       <c r="C10" s="55"/>
       <c r="D10" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E10" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F10" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G10" s="55"/>
       <c r="H10" s="55"/>
@@ -35447,30 +35520,30 @@
         <v>0.0</v>
       </c>
       <c r="T10" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U10" s="55"/>
       <c r="V10" s="55"/>
       <c r="W10" s="54" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="X10" s="55"/>
       <c r="Y10" s="55"/>
     </row>
     <row r="11">
       <c r="A11" s="54" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B11" s="55"/>
       <c r="C11" s="55"/>
       <c r="D11" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E11" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F11" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G11" s="55"/>
       <c r="H11" s="55"/>
@@ -35490,30 +35563,30 @@
         <v>0.0</v>
       </c>
       <c r="T11" s="54" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U11" s="55"/>
       <c r="V11" s="55"/>
       <c r="W11" s="54" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="X11" s="55"/>
       <c r="Y11" s="55"/>
     </row>
     <row r="12">
       <c r="A12" s="54" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B12" s="55"/>
       <c r="C12" s="55"/>
       <c r="D12" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E12" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F12" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G12" s="54"/>
       <c r="H12" s="55"/>
@@ -35533,30 +35606,30 @@
         <v>900.0</v>
       </c>
       <c r="T12" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U12" s="54"/>
       <c r="V12" s="55"/>
       <c r="W12" s="54" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="X12" s="55"/>
       <c r="Y12" s="55"/>
     </row>
     <row r="13">
       <c r="A13" s="54" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B13" s="55"/>
       <c r="C13" s="55"/>
       <c r="D13" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E13" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F13" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G13" s="54"/>
       <c r="H13" s="55"/>
@@ -35576,30 +35649,30 @@
         <v>200.0</v>
       </c>
       <c r="T13" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U13" s="54"/>
       <c r="V13" s="55"/>
       <c r="W13" s="54" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="X13" s="55"/>
       <c r="Y13" s="55"/>
     </row>
     <row r="14">
       <c r="A14" s="54" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B14" s="55"/>
       <c r="C14" s="55"/>
       <c r="D14" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E14" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F14" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G14" s="54"/>
       <c r="H14" s="55"/>
@@ -35619,30 +35692,30 @@
         <v>21.57</v>
       </c>
       <c r="T14" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U14" s="54"/>
       <c r="V14" s="55"/>
       <c r="W14" s="54" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="X14" s="55"/>
       <c r="Y14" s="55"/>
     </row>
     <row r="15">
       <c r="A15" s="54" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B15" s="55"/>
       <c r="C15" s="55"/>
       <c r="D15" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E15" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F15" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G15" s="54"/>
       <c r="H15" s="55"/>
@@ -35662,30 +35735,30 @@
         <v>42.0</v>
       </c>
       <c r="T15" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U15" s="54"/>
       <c r="V15" s="55"/>
       <c r="W15" s="54" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="X15" s="55"/>
       <c r="Y15" s="55"/>
     </row>
     <row r="16">
       <c r="A16" s="54" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B16" s="55"/>
       <c r="C16" s="55"/>
       <c r="D16" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E16" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F16" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G16" s="54"/>
       <c r="H16" s="55"/>
@@ -35705,30 +35778,30 @@
         <v>5.5</v>
       </c>
       <c r="T16" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U16" s="54"/>
       <c r="V16" s="55"/>
       <c r="W16" s="54" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="X16" s="55"/>
       <c r="Y16" s="55"/>
     </row>
     <row r="17">
       <c r="A17" s="54" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B17" s="55"/>
       <c r="C17" s="55"/>
       <c r="D17" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E17" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F17" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G17" s="54"/>
       <c r="H17" s="55"/>
@@ -35748,30 +35821,30 @@
         <v>13.32</v>
       </c>
       <c r="T17" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U17" s="54"/>
       <c r="V17" s="55"/>
       <c r="W17" s="54" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="X17" s="55"/>
       <c r="Y17" s="55"/>
     </row>
     <row r="18">
       <c r="A18" s="54" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B18" s="55"/>
       <c r="C18" s="55"/>
       <c r="D18" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E18" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F18" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G18" s="54"/>
       <c r="H18" s="55"/>
@@ -35791,30 +35864,30 @@
         <v>4.75</v>
       </c>
       <c r="T18" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U18" s="54"/>
       <c r="V18" s="55"/>
       <c r="W18" s="54" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X18" s="55"/>
       <c r="Y18" s="55"/>
     </row>
     <row r="19">
       <c r="A19" s="54" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B19" s="55"/>
       <c r="C19" s="55"/>
       <c r="D19" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E19" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F19" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G19" s="54"/>
       <c r="H19" s="55"/>
@@ -35834,30 +35907,30 @@
         <v>25.79</v>
       </c>
       <c r="T19" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U19" s="54"/>
       <c r="V19" s="55"/>
       <c r="W19" s="54" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="X19" s="55"/>
       <c r="Y19" s="55"/>
     </row>
     <row r="20">
       <c r="A20" s="54" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B20" s="55"/>
       <c r="C20" s="55"/>
       <c r="D20" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E20" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F20" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G20" s="54"/>
       <c r="H20" s="55"/>
@@ -35877,30 +35950,30 @@
         <v>33.27</v>
       </c>
       <c r="T20" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U20" s="54"/>
       <c r="V20" s="55"/>
       <c r="W20" s="54" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X20" s="55"/>
       <c r="Y20" s="55"/>
     </row>
     <row r="21">
       <c r="A21" s="54" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B21" s="55"/>
       <c r="C21" s="55"/>
       <c r="D21" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E21" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F21" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G21" s="54"/>
       <c r="H21" s="55"/>
@@ -35920,30 +35993,30 @@
         <v>28.85</v>
       </c>
       <c r="T21" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U21" s="54"/>
       <c r="V21" s="55"/>
       <c r="W21" s="54" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="X21" s="55"/>
       <c r="Y21" s="55"/>
     </row>
     <row r="22">
       <c r="A22" s="54" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B22" s="55"/>
       <c r="C22" s="55"/>
       <c r="D22" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E22" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F22" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G22" s="54"/>
       <c r="H22" s="55"/>
@@ -35963,30 +36036,30 @@
         <v>19.5</v>
       </c>
       <c r="T22" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U22" s="54"/>
       <c r="V22" s="55"/>
       <c r="W22" s="54" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X22" s="55"/>
       <c r="Y22" s="55"/>
     </row>
     <row r="23">
       <c r="A23" s="54" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B23" s="55"/>
       <c r="C23" s="55"/>
       <c r="D23" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E23" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F23" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G23" s="54"/>
       <c r="H23" s="55"/>
@@ -36006,30 +36079,30 @@
         <v>14.5</v>
       </c>
       <c r="T23" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U23" s="54"/>
       <c r="V23" s="55"/>
       <c r="W23" s="54" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="X23" s="55"/>
       <c r="Y23" s="55"/>
     </row>
     <row r="24">
       <c r="A24" s="54" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B24" s="55"/>
       <c r="C24" s="55"/>
       <c r="D24" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E24" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F24" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G24" s="54"/>
       <c r="H24" s="55"/>
@@ -36049,30 +36122,30 @@
         <v>3.98</v>
       </c>
       <c r="T24" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U24" s="54"/>
       <c r="V24" s="55"/>
       <c r="W24" s="54" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="X24" s="55"/>
       <c r="Y24" s="55"/>
     </row>
     <row r="25">
       <c r="A25" s="54" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B25" s="55"/>
       <c r="C25" s="55"/>
       <c r="D25" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E25" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F25" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G25" s="54"/>
       <c r="H25" s="55"/>
@@ -36092,30 +36165,30 @@
         <v>39.92</v>
       </c>
       <c r="T25" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U25" s="54"/>
       <c r="V25" s="55"/>
       <c r="W25" s="54" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="X25" s="55"/>
       <c r="Y25" s="55"/>
     </row>
     <row r="26">
       <c r="A26" s="54" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B26" s="55"/>
       <c r="C26" s="55"/>
       <c r="D26" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E26" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F26" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G26" s="54"/>
       <c r="H26" s="55"/>
@@ -36135,30 +36208,30 @@
         <v>16.48</v>
       </c>
       <c r="T26" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U26" s="54"/>
       <c r="V26" s="55"/>
       <c r="W26" s="54" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="X26" s="55"/>
       <c r="Y26" s="55"/>
     </row>
     <row r="27">
       <c r="A27" s="54" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B27" s="55"/>
       <c r="C27" s="55"/>
       <c r="D27" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E27" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F27" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G27" s="54"/>
       <c r="H27" s="55"/>
@@ -36178,30 +36251,30 @@
         <v>41.25</v>
       </c>
       <c r="T27" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U27" s="54"/>
       <c r="V27" s="55"/>
       <c r="W27" s="54" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X27" s="55"/>
       <c r="Y27" s="55"/>
     </row>
     <row r="28">
       <c r="A28" s="54" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B28" s="55"/>
       <c r="C28" s="55"/>
       <c r="D28" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E28" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F28" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G28" s="54"/>
       <c r="H28" s="55"/>
@@ -36221,30 +36294,30 @@
         <v>3.33</v>
       </c>
       <c r="T28" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U28" s="54"/>
       <c r="V28" s="55"/>
       <c r="W28" s="54" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="X28" s="55"/>
       <c r="Y28" s="55"/>
     </row>
     <row r="29">
       <c r="A29" s="54" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B29" s="55"/>
       <c r="C29" s="55"/>
       <c r="D29" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E29" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F29" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G29" s="54"/>
       <c r="H29" s="55"/>
@@ -36264,30 +36337,30 @@
         <v>6.18</v>
       </c>
       <c r="T29" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U29" s="54"/>
       <c r="V29" s="55"/>
       <c r="W29" s="54" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="X29" s="55"/>
       <c r="Y29" s="55"/>
     </row>
     <row r="30">
       <c r="A30" s="54" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B30" s="55"/>
       <c r="C30" s="55"/>
       <c r="D30" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E30" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F30" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G30" s="54"/>
       <c r="H30" s="55"/>
@@ -36307,30 +36380,30 @@
         <v>10.66</v>
       </c>
       <c r="T30" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U30" s="54"/>
       <c r="V30" s="55"/>
       <c r="W30" s="54" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="X30" s="55"/>
       <c r="Y30" s="55"/>
     </row>
     <row r="31">
       <c r="A31" s="54" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B31" s="55"/>
       <c r="C31" s="55"/>
       <c r="D31" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E31" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F31" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G31" s="54"/>
       <c r="H31" s="55"/>
@@ -36350,30 +36423,30 @@
         <v>9.5</v>
       </c>
       <c r="T31" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U31" s="54"/>
       <c r="V31" s="55"/>
       <c r="W31" s="54" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="X31" s="55"/>
       <c r="Y31" s="55"/>
     </row>
     <row r="32">
       <c r="A32" s="54" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B32" s="55"/>
       <c r="C32" s="55"/>
       <c r="D32" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E32" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G32" s="54"/>
       <c r="H32" s="55"/>
@@ -36393,30 +36466,30 @@
         <v>8.0</v>
       </c>
       <c r="T32" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U32" s="54"/>
       <c r="V32" s="55"/>
       <c r="W32" s="54" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="X32" s="55"/>
       <c r="Y32" s="55"/>
     </row>
     <row r="33">
       <c r="A33" s="54" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B33" s="55"/>
       <c r="C33" s="55"/>
       <c r="D33" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E33" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F33" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G33" s="54"/>
       <c r="H33" s="55"/>
@@ -36436,30 +36509,30 @@
         <v>51.17</v>
       </c>
       <c r="T33" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U33" s="54"/>
       <c r="V33" s="55"/>
       <c r="W33" s="54" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="X33" s="55"/>
       <c r="Y33" s="55"/>
     </row>
     <row r="34">
       <c r="A34" s="54" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B34" s="55"/>
       <c r="C34" s="55"/>
       <c r="D34" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E34" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G34" s="54"/>
       <c r="H34" s="55"/>
@@ -36479,30 +36552,30 @@
         <v>46.43</v>
       </c>
       <c r="T34" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U34" s="54"/>
       <c r="V34" s="55"/>
       <c r="W34" s="54" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="X34" s="55"/>
       <c r="Y34" s="55"/>
     </row>
     <row r="35">
       <c r="A35" s="54" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B35" s="55"/>
       <c r="C35" s="55"/>
       <c r="D35" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E35" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F35" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G35" s="54"/>
       <c r="H35" s="55"/>
@@ -36522,30 +36595,30 @@
         <v>4.6</v>
       </c>
       <c r="T35" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U35" s="54"/>
       <c r="V35" s="55"/>
       <c r="W35" s="54" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="X35" s="55"/>
       <c r="Y35" s="55"/>
     </row>
     <row r="36">
       <c r="A36" s="54" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B36" s="55"/>
       <c r="C36" s="55"/>
       <c r="D36" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E36" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F36" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G36" s="54"/>
       <c r="H36" s="55"/>
@@ -36565,30 +36638,30 @@
         <v>17.08</v>
       </c>
       <c r="T36" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U36" s="54"/>
       <c r="V36" s="55"/>
       <c r="W36" s="54" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="X36" s="55"/>
       <c r="Y36" s="55"/>
     </row>
     <row r="37">
       <c r="A37" s="54" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B37" s="55"/>
       <c r="C37" s="55"/>
       <c r="D37" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E37" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G37" s="54"/>
       <c r="H37" s="55"/>
@@ -36608,30 +36681,30 @@
         <v>95.0</v>
       </c>
       <c r="T37" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U37" s="54"/>
       <c r="V37" s="55"/>
       <c r="W37" s="54" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="X37" s="55"/>
       <c r="Y37" s="55"/>
     </row>
     <row r="38">
       <c r="A38" s="54" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B38" s="55"/>
       <c r="C38" s="55"/>
       <c r="D38" s="54" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E38" s="54" t="s">
         <v>506</v>
       </c>
       <c r="F38" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G38" s="54"/>
       <c r="H38" s="55"/>
@@ -36651,12 +36724,12 @@
         <v>6.05</v>
       </c>
       <c r="T38" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="U38" s="54"/>
       <c r="V38" s="55"/>
       <c r="W38" s="54" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="X38" s="55"/>
       <c r="Y38" s="55"/>
@@ -36685,24 +36758,24 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="57" t="s">
+        <v>786</v>
+      </c>
+      <c r="B1" s="58" t="s">
         <v>787</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="C1" s="58" t="s">
         <v>788</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="D1" s="57" t="s">
         <v>789</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="E1" s="58" t="s">
         <v>790</v>
-      </c>
-      <c r="E1" s="58" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="59" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
@@ -36747,7 +36820,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="59" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B5" s="65" t="s">
         <v>41</v>
@@ -36764,7 +36837,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="59" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B6" s="60"/>
       <c r="C6" s="61"/>
@@ -36775,7 +36848,7 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="59" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>49</v>
@@ -36792,7 +36865,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="59" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>154</v>
@@ -36809,7 +36882,7 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="59" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>51</v>
@@ -36826,7 +36899,7 @@
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="59" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B10" s="60"/>
       <c r="C10" s="61"/>
@@ -36837,7 +36910,7 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="59" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B11" s="65" t="s">
         <v>29</v>
@@ -36854,7 +36927,7 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="59" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B12" s="65" t="s">
         <v>154</v>
@@ -36871,7 +36944,7 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="59" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B13" s="65" t="s">
         <v>31</v>
@@ -36888,7 +36961,7 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="59" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B14" s="60"/>
       <c r="C14" s="61"/>
@@ -36899,7 +36972,7 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="59" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B15" s="65" t="s">
         <v>463</v>
@@ -36916,7 +36989,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="59" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>473</v>
@@ -36933,7 +37006,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="59" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>444</v>
@@ -36950,7 +37023,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="59" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B18" s="60"/>
       <c r="C18" s="61"/>
@@ -36961,7 +37034,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="59" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B19" s="65" t="s">
         <v>463</v>
@@ -36978,7 +37051,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="59" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B20" s="65" t="s">
         <v>467</v>
@@ -36995,7 +37068,7 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="59" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>444</v>
@@ -37012,7 +37085,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="59" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B22" s="60"/>
       <c r="C22" s="61"/>
@@ -37023,7 +37096,7 @@
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="59" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B23" s="65" t="s">
         <v>463</v>
@@ -37040,7 +37113,7 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="59" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>470</v>
@@ -37057,7 +37130,7 @@
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="59" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>444</v>
@@ -37094,11 +37167,11 @@
   <sheetData>
     <row r="1" ht="161.25" customHeight="1">
       <c r="A1" s="68" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="69" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -37310,7 +37383,7 @@
     </row>
     <row r="7">
       <c r="A7" s="71" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B7" s="72" t="s">
         <v>92</v>
@@ -37320,7 +37393,7 @@
       </c>
       <c r="D7" s="55"/>
       <c r="E7" s="72" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F7" s="55"/>
       <c r="G7" s="72" t="s">
@@ -37376,7 +37449,7 @@
     </row>
     <row r="9">
       <c r="A9" s="71" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B9" s="72" t="s">
         <v>129</v>
@@ -37518,7 +37591,7 @@
     </row>
     <row r="13">
       <c r="A13" s="71" t="s">
-        <v>181</v>
+        <v>814</v>
       </c>
       <c r="B13" s="72" t="s">
         <v>182</v>
@@ -37528,7 +37601,7 @@
       </c>
       <c r="D13" s="55"/>
       <c r="E13" s="72" t="s">
-        <v>181</v>
+        <v>814</v>
       </c>
       <c r="F13" s="55"/>
       <c r="G13" s="72" t="s">
@@ -37555,7 +37628,7 @@
     </row>
     <row r="14">
       <c r="A14" s="71" t="s">
-        <v>183</v>
+        <v>815</v>
       </c>
       <c r="B14" s="72" t="s">
         <v>184</v>
@@ -37565,7 +37638,7 @@
       </c>
       <c r="D14" s="55"/>
       <c r="E14" s="72" t="s">
-        <v>183</v>
+        <v>815</v>
       </c>
       <c r="F14" s="55"/>
       <c r="G14" s="72" t="s">
@@ -37699,7 +37772,7 @@
     </row>
     <row r="18">
       <c r="A18" s="71" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B18" s="72" t="s">
         <v>209</v>
@@ -37709,7 +37782,7 @@
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="72" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="72" t="s">
@@ -37989,7 +38062,7 @@
     </row>
     <row r="26">
       <c r="A26" s="71" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B26" s="72" t="s">
         <v>260</v>
@@ -37999,7 +38072,7 @@
       </c>
       <c r="D26" s="55"/>
       <c r="E26" s="72" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F26" s="55"/>
       <c r="G26" s="72" t="s">
@@ -38625,7 +38698,7 @@
     </row>
     <row r="44">
       <c r="A44" s="71" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B44" s="72" t="s">
         <v>331</v>
@@ -39210,13 +39283,13 @@
     </row>
     <row r="61">
       <c r="A61" s="71" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B61" s="72"/>
       <c r="C61" s="72"/>
       <c r="D61" s="55"/>
       <c r="E61" s="72" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F61" s="55"/>
       <c r="G61" s="72"/>
